--- a/scripts/metadata-by-id-adder-boa.xlsx
+++ b/scripts/metadata-by-id-adder-boa.xlsx
@@ -1,19 +1,23 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mx="http://schemas.microsoft.com/office/mac/excel/2008/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:mv="urn:schemas-microsoft-com:mac:vml" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xm="http://schemas.microsoft.com/office/excel/2006/main">
+<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
+  <fileVersion rupBuild="9303" lowestEdited="5" lastEdited="5" appName="xl"/>
   <workbookPr/>
+  <bookViews>
+    <workbookView xWindow="480" yWindow="60" windowWidth="18195" windowHeight="8505" activeTab="0"/>
+  </bookViews>
   <sheets>
-    <sheet state="visible" name="Sheet1" sheetId="1" r:id="rId5"/>
+    <sheet r:id="rId1" sheetId="1" name="Sheet1"/>
   </sheets>
   <definedNames>
-    <definedName hidden="1" localSheetId="0" name="_xlnm._FilterDatabase">Sheet1!$A$1:$F$92</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="0">Sheet1!$A$1:$F$92</definedName>
   </definedNames>
-  <calcPr/>
+  <calcPr fullCalcOnLoad="1"/>
 </workbook>
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="413" uniqueCount="308">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="414" uniqueCount="309">
   <si>
     <t>ID</t>
   </si>
@@ -188,7 +192,7 @@
     "id": "12611",
     "type": "Act",
     "class": "Mythos",
-    "cycle": "Core 2026"
+    "cycle": "Core 2026",
     "clueThresholdPerInvestigator": 3
 }</t>
   </si>
@@ -340,7 +344,7 @@
     },
     "locationBack": {
       "icons":"Triangle",
-      "connections":"Spade|Plus","
+      "connections":"Spade|Plus",
     }, 
 }
 </t>
@@ -1126,7 +1130,7 @@
     },
     "locationBack": {
      "icons":"Square",
-     "connections":"Circle|Plus|Hourglass
+     "connections":"Circle|Plus|Hourglass"
     }
  }
 </t>
@@ -1654,6 +1658,9 @@
     <t>Collector</t>
   </si>
   <si>
+    <t>{}</t>
+  </si>
+  <si>
     <t>Reward</t>
   </si>
   <si>
@@ -1962,22 +1969,21 @@
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
-<styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
-  <fonts count="3">
+<styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" mc:Ignorable="x14ac">
+  <numFmts count="0"/>
+  <fonts count="2" x14ac:knownFonts="1">
     <font>
-      <sz val="10.0"/>
-      <color rgb="FF000000"/>
-      <name val="Arial"/>
+      <sz val="11"/>
+      <color theme="1"/>
+      <name val="Calibri"/>
+      <family val="2"/>
       <scheme val="minor"/>
     </font>
     <font>
-      <color theme="1"/>
+      <sz val="11"/>
+      <color rgb="FF000000"/>
       <name val="Arial"/>
-    </font>
-    <font>
-      <color theme="1"/>
-      <name val="Arial"/>
-      <scheme val="minor"/>
+      <family val="2"/>
     </font>
   </fonts>
   <fills count="2">
@@ -1985,142 +1991,71 @@
       <patternFill patternType="none"/>
     </fill>
     <fill>
-      <patternFill patternType="lightGray"/>
+      <patternFill patternType="gray125"/>
     </fill>
   </fills>
-  <borders count="1">
-    <border/>
+  <borders count="2">
+    <border>
+      <left/>
+      <right/>
+      <top/>
+      <bottom/>
+      <diagonal/>
+    </border>
+    <border>
+      <left/>
+      <right/>
+      <top/>
+      <bottom/>
+      <diagonal/>
+    </border>
   </borders>
   <cellStyleXfs count="1">
-    <xf borderId="0" fillId="0" fontId="0" numFmtId="0" applyAlignment="1" applyFont="1"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="15">
-    <xf borderId="0" fillId="0" fontId="0" numFmtId="0" xfId="0" applyAlignment="1" applyFont="1">
-      <alignment readingOrder="0" shrinkToFit="0" vertical="bottom" wrapText="0"/>
+  <cellXfs count="9">
+    <xf xfId="0" numFmtId="0" borderId="0" fontId="0" fillId="0"/>
+    <xf xfId="0" numFmtId="49" applyNumberFormat="1" borderId="1" applyBorder="1" fontId="1" applyFont="1" fillId="0" applyAlignment="1">
+      <alignment horizontal="center"/>
     </xf>
-    <xf borderId="0" fillId="0" fontId="1" numFmtId="0" xfId="0" applyAlignment="1" applyFont="1">
-      <alignment horizontal="center" readingOrder="0" shrinkToFit="0" vertical="center" wrapText="0"/>
+    <xf xfId="0" numFmtId="0" borderId="1" applyBorder="1" fontId="1" applyFont="1" fillId="0" applyAlignment="1">
+      <alignment horizontal="left" wrapText="1"/>
     </xf>
-    <xf borderId="0" fillId="0" fontId="2" numFmtId="49" xfId="0" applyAlignment="1" applyFont="1" applyNumberFormat="1">
-      <alignment horizontal="left" readingOrder="0" shrinkToFit="0" vertical="center" wrapText="1"/>
+    <xf xfId="0" numFmtId="0" borderId="1" applyBorder="1" fontId="1" applyFont="1" fillId="0" applyAlignment="1">
+      <alignment horizontal="left"/>
     </xf>
-    <xf borderId="0" fillId="0" fontId="2" numFmtId="0" xfId="0" applyAlignment="1" applyFont="1">
-      <alignment horizontal="left" readingOrder="0" shrinkToFit="0" vertical="center" wrapText="0"/>
+    <xf xfId="0" numFmtId="3" applyNumberFormat="1" borderId="1" applyBorder="1" fontId="1" applyFont="1" fillId="0" applyAlignment="1">
+      <alignment horizontal="right"/>
     </xf>
-    <xf borderId="0" fillId="0" fontId="2" numFmtId="0" xfId="0" applyAlignment="1" applyFont="1">
-      <alignment horizontal="left" readingOrder="0" shrinkToFit="0" vertical="center" wrapText="1"/>
+    <xf xfId="0" numFmtId="49" applyNumberFormat="1" borderId="0" fontId="0" fillId="0" applyAlignment="1">
+      <alignment horizontal="center"/>
     </xf>
-    <xf borderId="0" fillId="0" fontId="1" numFmtId="49" xfId="0" applyAlignment="1" applyFont="1" applyNumberFormat="1">
-      <alignment horizontal="center" readingOrder="0" shrinkToFit="0" vertical="bottom" wrapText="0"/>
+    <xf xfId="0" numFmtId="0" borderId="0" fontId="0" fillId="0" applyAlignment="1">
+      <alignment horizontal="left" wrapText="1"/>
     </xf>
-    <xf borderId="0" fillId="0" fontId="2" numFmtId="0" xfId="0" applyAlignment="1" applyFont="1">
-      <alignment readingOrder="0" shrinkToFit="0" vertical="center" wrapText="1"/>
+    <xf xfId="0" numFmtId="0" borderId="0" fontId="0" fillId="0" applyAlignment="1">
+      <alignment horizontal="left"/>
     </xf>
-    <xf borderId="0" fillId="0" fontId="2" numFmtId="0" xfId="0" applyAlignment="1" applyFont="1">
-      <alignment readingOrder="0" shrinkToFit="0" vertical="center" wrapText="0"/>
-    </xf>
-    <xf borderId="0" fillId="0" fontId="2" numFmtId="49" xfId="0" applyAlignment="1" applyFont="1" applyNumberFormat="1">
-      <alignment readingOrder="0" shrinkToFit="0" vertical="center" wrapText="0"/>
-    </xf>
-    <xf borderId="0" fillId="0" fontId="2" numFmtId="0" xfId="0" applyAlignment="1" applyFont="1">
-      <alignment shrinkToFit="0" vertical="center" wrapText="1"/>
-    </xf>
-    <xf borderId="0" fillId="0" fontId="1" numFmtId="0" xfId="0" applyAlignment="1" applyFont="1">
-      <alignment readingOrder="0" shrinkToFit="0" vertical="bottom" wrapText="0"/>
-    </xf>
-    <xf borderId="0" fillId="0" fontId="2" numFmtId="0" xfId="0" applyAlignment="1" applyFont="1">
-      <alignment readingOrder="0" shrinkToFit="0" vertical="center" wrapText="1"/>
-    </xf>
-    <xf borderId="0" fillId="0" fontId="1" numFmtId="49" xfId="0" applyAlignment="1" applyFont="1" applyNumberFormat="1">
-      <alignment readingOrder="0" shrinkToFit="0" vertical="bottom" wrapText="0"/>
-    </xf>
-    <xf borderId="0" fillId="0" fontId="1" numFmtId="49" xfId="0" applyAlignment="1" applyFont="1" applyNumberFormat="1">
-      <alignment shrinkToFit="0" vertical="bottom" wrapText="0"/>
-    </xf>
-    <xf borderId="0" fillId="0" fontId="2" numFmtId="49" xfId="0" applyAlignment="1" applyFont="1" applyNumberFormat="1">
-      <alignment shrinkToFit="0" vertical="center" wrapText="0"/>
+    <xf xfId="0" numFmtId="0" borderId="0" fontId="0" fillId="0" applyAlignment="1">
+      <alignment horizontal="right"/>
     </xf>
   </cellXfs>
   <cellStyles count="1">
-    <cellStyle xfId="0" name="Normal" builtinId="0"/>
+    <cellStyle xfId="0" builtinId="0" name="Normal"/>
   </cellStyles>
-  <dxfs count="5">
-    <dxf>
-      <font/>
-      <fill>
-        <patternFill patternType="none"/>
-      </fill>
-      <border/>
-    </dxf>
-    <dxf>
-      <font/>
-      <fill>
-        <patternFill patternType="solid">
-          <fgColor rgb="FF356854"/>
-          <bgColor rgb="FF356854"/>
-        </patternFill>
-      </fill>
-      <border/>
-    </dxf>
-    <dxf>
-      <font/>
-      <fill>
-        <patternFill patternType="solid">
-          <fgColor rgb="FFFFFFFF"/>
-          <bgColor rgb="FFFFFFFF"/>
-        </patternFill>
-      </fill>
-      <border/>
-    </dxf>
-    <dxf>
-      <font/>
-      <fill>
-        <patternFill patternType="solid">
-          <fgColor rgb="FFF6F8F9"/>
-          <bgColor rgb="FFF6F8F9"/>
-        </patternFill>
-      </fill>
-      <border/>
-    </dxf>
-    <dxf>
-      <border>
-        <left style="thin">
-          <color rgb="FF356854"/>
-        </left>
-        <right style="thin">
-          <color rgb="FF356854"/>
-        </right>
-        <top style="thin">
-          <color rgb="FF356854"/>
-        </top>
-        <bottom style="thin">
-          <color rgb="FF356854"/>
-        </bottom>
-      </border>
-    </dxf>
-  </dxfs>
-  <tableStyles count="1">
-    <tableStyle count="4" pivot="0" name="Sheet1-style">
-      <tableStyleElement dxfId="1" type="headerRow"/>
-      <tableStyleElement dxfId="2" type="firstRowStripe"/>
-      <tableStyleElement dxfId="3" type="secondRowStripe"/>
-      <tableStyleElement dxfId="4" size="0" type="wholeTable"/>
-    </tableStyle>
-  </tableStyles>
+  <dxfs count="0"/>
+  <tableStyles count="0" defaultTableStyle="TableStyleMedium9" defaultPivotStyle="PivotStyleLight16"/>
+  <extLst>
+    <ext uri="{EB79DEF2-80B8-43e5-95BD-54CBDDF9020C}">
+      <x14ac:slicerStyles xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" defaultSlicerStyle="SlicerStyleLight1"/>
+    </ext>
+  </extLst>
 </styleSheet>
 </file>
 
-<file path=xl/drawings/drawing1.xml><?xml version="1.0" encoding="utf-8"?>
-<xdr:wsDr xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:c="http://schemas.openxmlformats.org/drawingml/2006/chart" xmlns:cx="http://schemas.microsoft.com/office/drawing/2014/chartex" xmlns:cx1="http://schemas.microsoft.com/office/drawing/2015/9/8/chartex" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:dgm="http://schemas.openxmlformats.org/drawingml/2006/diagram" xmlns:x3Unk="http://schemas.microsoft.com/office/drawing/2010/slicer" xmlns:sle15="http://schemas.microsoft.com/office/drawing/2012/slicer"/>
-</file>
-
-<file path=xl/persons/person.xml><?xml version="1.0" encoding="utf-8"?>
-<x18tc:personList xmlns:x18tc="http://schemas.microsoft.com/office/spreadsheetml/2018/threadedcomments"/>
-</file>
-
 <file path=xl/tables/table1.xml><?xml version="1.0" encoding="utf-8"?>
-<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" ref="A1:F92" displayName="Table1" name="Table1" id="1">
-  <autoFilter ref="$A$1:$F$92"/>
+<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" ref="A1:F92" displayName="Table1" name="Table1" id="1" totalsRowShown="0">
+  <autoFilter ref="A1:F92"/>
   <tableColumns count="6">
     <tableColumn name="ID" id="1"/>
     <tableColumn name="Type" id="2"/>
@@ -2129,19 +2064,19 @@
     <tableColumn name="Metadata" id="5"/>
     <tableColumn name="Comments" id="6"/>
   </tableColumns>
-  <tableStyleInfo name="Sheet1-style" showColumnStripes="0" showFirstColumn="1" showLastColumn="1" showRowStripes="1"/>
+  <tableStyleInfo name="TableStyleLight1" showColumnStripes="0" showRowStripes="1" showLastColumn="1" showFirstColumn="1"/>
 </table>
 </file>
 
 <file path=xl/theme/theme1.xml><?xml version="1.0" encoding="utf-8"?>
-<a:theme xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Sheets">
+<a:theme xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" name="Office Theme">
   <a:themeElements>
-    <a:clrScheme name="Sheets">
+    <a:clrScheme name="Office">
       <a:dk1>
-        <a:srgbClr val="000000"/>
+        <a:sysClr lastClr="000000" val="windowText"/>
       </a:dk1>
       <a:lt1>
-        <a:srgbClr val="FFFFFF"/>
+        <a:sysClr lastClr="FFFFFF" val="window"/>
       </a:lt1>
       <a:dk2>
         <a:srgbClr val="000000"/>
@@ -2168,22 +2103,82 @@
         <a:srgbClr val="46BDC6"/>
       </a:accent6>
       <a:hlink>
-        <a:srgbClr val="1155CC"/>
+        <a:srgbClr val="0000FF"/>
       </a:hlink>
       <a:folHlink>
-        <a:srgbClr val="1155CC"/>
+        <a:srgbClr val="800080"/>
       </a:folHlink>
     </a:clrScheme>
-    <a:fontScheme name="Sheets">
+    <a:fontScheme name="Office">
       <a:majorFont>
-        <a:latin typeface="Arial"/>
-        <a:ea typeface="Arial"/>
-        <a:cs typeface="Arial"/>
+        <a:latin typeface="Cambria"/>
+        <a:ea typeface=""/>
+        <a:cs typeface=""/>
+        <a:font typeface="ＭＳ Ｐゴシック" script="Jpan"/>
+        <a:font typeface="맑은 고딕" script="Hang"/>
+        <a:font typeface="宋体" script="Hans"/>
+        <a:font typeface="新細明體" script="Hant"/>
+        <a:font typeface="Times New Roman" script="Arab"/>
+        <a:font typeface="Times New Roman" script="Hebr"/>
+        <a:font typeface="Tahoma" script="Thai"/>
+        <a:font typeface="Nyala" script="Ethi"/>
+        <a:font typeface="Vrinda" script="Beng"/>
+        <a:font typeface="Shruti" script="Gujr"/>
+        <a:font typeface="MoolBoran" script="Khmr"/>
+        <a:font typeface="Tunga" script="Knda"/>
+        <a:font typeface="Raavi" script="Guru"/>
+        <a:font typeface="Euphemia" script="Cans"/>
+        <a:font typeface="Plantagenet Cherokee" script="Cher"/>
+        <a:font typeface="Microsoft Yi Baiti" script="Yiii"/>
+        <a:font typeface="Microsoft Himalaya" script="Tibt"/>
+        <a:font typeface="MV Boli" script="Thaa"/>
+        <a:font typeface="Mangal" script="Deva"/>
+        <a:font typeface="Gautami" script="Telu"/>
+        <a:font typeface="Latha" script="Taml"/>
+        <a:font typeface="Estrangelo Edessa" script="Syrc"/>
+        <a:font typeface="Kalinga" script="Orya"/>
+        <a:font typeface="Kartika" script="Mlym"/>
+        <a:font typeface="DokChampa" script="Laoo"/>
+        <a:font typeface="Iskoola Pota" script="Sinh"/>
+        <a:font typeface="Mongolian Baiti" script="Mong"/>
+        <a:font typeface="Times New Roman" script="Viet"/>
+        <a:font typeface="Microsoft Uighur" script="Uigh"/>
+        <a:font typeface="Sylfaen" script="Geor"/>
       </a:majorFont>
       <a:minorFont>
-        <a:latin typeface="Arial"/>
-        <a:ea typeface="Arial"/>
-        <a:cs typeface="Arial"/>
+        <a:latin typeface="Calibri"/>
+        <a:ea typeface=""/>
+        <a:cs typeface=""/>
+        <a:font typeface="ＭＳ Ｐゴシック" script="Jpan"/>
+        <a:font typeface="맑은 고딕" script="Hang"/>
+        <a:font typeface="宋体" script="Hans"/>
+        <a:font typeface="新細明體" script="Hant"/>
+        <a:font typeface="Arial" script="Arab"/>
+        <a:font typeface="Arial" script="Hebr"/>
+        <a:font typeface="Tahoma" script="Thai"/>
+        <a:font typeface="Nyala" script="Ethi"/>
+        <a:font typeface="Vrinda" script="Beng"/>
+        <a:font typeface="Shruti" script="Gujr"/>
+        <a:font typeface="DaunPenh" script="Khmr"/>
+        <a:font typeface="Tunga" script="Knda"/>
+        <a:font typeface="Raavi" script="Guru"/>
+        <a:font typeface="Euphemia" script="Cans"/>
+        <a:font typeface="Plantagenet Cherokee" script="Cher"/>
+        <a:font typeface="Microsoft Yi Baiti" script="Yiii"/>
+        <a:font typeface="Microsoft Himalaya" script="Tibt"/>
+        <a:font typeface="MV Boli" script="Thaa"/>
+        <a:font typeface="Mangal" script="Deva"/>
+        <a:font typeface="Gautami" script="Telu"/>
+        <a:font typeface="Latha" script="Taml"/>
+        <a:font typeface="Estrangelo Edessa" script="Syrc"/>
+        <a:font typeface="Kalinga" script="Orya"/>
+        <a:font typeface="Kartika" script="Mlym"/>
+        <a:font typeface="DokChampa" script="Laoo"/>
+        <a:font typeface="Iskoola Pota" script="Sinh"/>
+        <a:font typeface="Mongolian Baiti" script="Mong"/>
+        <a:font typeface="Arial" script="Viet"/>
+        <a:font typeface="Microsoft Uighur" script="Uigh"/>
+        <a:font typeface="Sylfaen" script="Geor"/>
       </a:minorFont>
     </a:fontScheme>
     <a:fmtScheme name="Office">
@@ -2195,154 +2190,184 @@
           <a:gsLst>
             <a:gs pos="0">
               <a:schemeClr val="phClr">
-                <a:lumMod val="110000"/>
-                <a:satMod val="105000"/>
-                <a:tint val="67000"/>
+                <a:tint val="50000"/>
+                <a:satMod val="300000"/>
               </a:schemeClr>
             </a:gs>
-            <a:gs pos="50000">
+            <a:gs pos="35000">
               <a:schemeClr val="phClr">
-                <a:lumMod val="105000"/>
-                <a:satMod val="103000"/>
-                <a:tint val="73000"/>
+                <a:tint val="37000"/>
+                <a:satMod val="300000"/>
               </a:schemeClr>
             </a:gs>
             <a:gs pos="100000">
               <a:schemeClr val="phClr">
-                <a:lumMod val="105000"/>
-                <a:satMod val="109000"/>
-                <a:tint val="81000"/>
+                <a:satMod val="350000"/>
               </a:schemeClr>
             </a:gs>
           </a:gsLst>
-          <a:lin ang="5400000" scaled="0"/>
+          <a:lin scaled="1" ang="16200000"/>
         </a:gradFill>
         <a:gradFill rotWithShape="1">
           <a:gsLst>
             <a:gs pos="0">
               <a:schemeClr val="phClr">
-                <a:satMod val="103000"/>
-                <a:lumMod val="102000"/>
-                <a:tint val="94000"/>
+                <a:tint val="51000"/>
+                <a:satMod val="130000"/>
               </a:schemeClr>
             </a:gs>
-            <a:gs pos="50000">
+            <a:gs pos="80000">
               <a:schemeClr val="phClr">
-                <a:satMod val="110000"/>
-                <a:lumMod val="100000"/>
-                <a:shade val="100000"/>
+                <a:tint val="15000"/>
+                <a:satMod val="130000"/>
               </a:schemeClr>
             </a:gs>
             <a:gs pos="100000">
               <a:schemeClr val="phClr">
-                <a:lumMod val="99000"/>
-                <a:satMod val="120000"/>
-                <a:shade val="78000"/>
+                <a:tint val="94000"/>
+                <a:satMod val="135000"/>
               </a:schemeClr>
             </a:gs>
           </a:gsLst>
-          <a:lin ang="5400000" scaled="0"/>
+          <a:lin scaled="1" ang="16200000"/>
         </a:gradFill>
       </a:fillStyleLst>
       <a:lnStyleLst>
-        <a:ln w="6350" cap="flat" cmpd="sng" algn="ctr">
+        <a:ln algn="ctr" cmpd="sng" cap="flat" w="9525">
+          <a:solidFill>
+            <a:schemeClr val="phClr">
+              <a:shade val="9500"/>
+              <a:satMod val="105000"/>
+            </a:schemeClr>
+          </a:solidFill>
+          <a:prstDash val="solid"/>
+        </a:ln>
+        <a:ln algn="ctr" cmpd="sng" cap="flat" w="25400">
           <a:solidFill>
             <a:schemeClr val="phClr"/>
           </a:solidFill>
           <a:prstDash val="solid"/>
-          <a:miter lim="800000"/>
         </a:ln>
-        <a:ln w="12700" cap="flat" cmpd="sng" algn="ctr">
+        <a:ln algn="ctr" cmpd="sng" cap="flat" w="38100">
           <a:solidFill>
             <a:schemeClr val="phClr"/>
           </a:solidFill>
           <a:prstDash val="solid"/>
-          <a:miter lim="800000"/>
-        </a:ln>
-        <a:ln w="19050" cap="flat" cmpd="sng" algn="ctr">
-          <a:solidFill>
-            <a:schemeClr val="phClr"/>
-          </a:solidFill>
-          <a:prstDash val="solid"/>
-          <a:miter lim="800000"/>
         </a:ln>
       </a:lnStyleLst>
       <a:effectStyleLst>
         <a:effectStyle>
-          <a:effectLst/>
-        </a:effectStyle>
-        <a:effectStyle>
-          <a:effectLst/>
+          <a:effectLst>
+            <a:outerShdw dir="5400000" rotWithShape="0" dist="23000" blurRad="40000">
+              <a:srgbClr val="000000">
+                <a:alpha val="38000"/>
+              </a:srgbClr>
+            </a:outerShdw>
+          </a:effectLst>
         </a:effectStyle>
         <a:effectStyle>
           <a:effectLst>
-            <a:outerShdw blurRad="57150" dist="19050" dir="5400000" algn="ctr" rotWithShape="0">
+            <a:outerShdw dir="5400000" rotWithShape="0" dist="23000" blurRad="40000">
               <a:srgbClr val="000000">
-                <a:alpha val="63000"/>
+                <a:alpha val="35000"/>
               </a:srgbClr>
             </a:outerShdw>
           </a:effectLst>
+        </a:effectStyle>
+        <a:effectStyle>
+          <a:effectLst>
+            <a:outerShdw dir="5400000" rotWithShape="0" dist="23000" blurRad="40000">
+              <a:srgbClr val="000000">
+                <a:alpha val="35000"/>
+              </a:srgbClr>
+            </a:outerShdw>
+          </a:effectLst>
+          <a:scene3d>
+            <a:camera prst="orthographicFront">
+              <a:rot rev="0" lon="0" lat="0"/>
+            </a:camera>
+            <a:lightRig dir="t" rig="threePt">
+              <a:rot rev="1200000" lon="0" lat="0"/>
+            </a:lightRig>
+          </a:scene3d>
+          <a:sp3d>
+            <a:bevelT w="63500" h="25400"/>
+          </a:sp3d>
         </a:effectStyle>
       </a:effectStyleLst>
       <a:bgFillStyleLst>
         <a:solidFill>
           <a:schemeClr val="phClr"/>
         </a:solidFill>
-        <a:solidFill>
-          <a:schemeClr val="phClr">
-            <a:tint val="95000"/>
-            <a:satMod val="170000"/>
-          </a:schemeClr>
-        </a:solidFill>
         <a:gradFill rotWithShape="1">
           <a:gsLst>
             <a:gs pos="0">
               <a:schemeClr val="phClr">
-                <a:tint val="93000"/>
-                <a:satMod val="150000"/>
-                <a:shade val="98000"/>
-                <a:lumMod val="102000"/>
+                <a:tint val="40000"/>
+                <a:satMod val="350000"/>
               </a:schemeClr>
             </a:gs>
-            <a:gs pos="50000">
+            <a:gs pos="40000">
               <a:schemeClr val="phClr">
-                <a:tint val="98000"/>
-                <a:satMod val="130000"/>
-                <a:shade val="90000"/>
-                <a:lumMod val="103000"/>
+                <a:tint val="45000"/>
+                <a:shade val="99000"/>
+                <a:satMod val="350000"/>
               </a:schemeClr>
             </a:gs>
             <a:gs pos="100000">
               <a:schemeClr val="phClr">
-                <a:shade val="63000"/>
-                <a:satMod val="120000"/>
+                <a:tint val="20000"/>
+                <a:satMod val="255000"/>
               </a:schemeClr>
             </a:gs>
           </a:gsLst>
-          <a:lin ang="5400000" scaled="0"/>
+          <a:path path="circle">
+            <a:fillToRect l="50000" t="-80000" r="50000" b="180000"/>
+          </a:path>
+        </a:gradFill>
+        <a:gradFill rotWithShape="1">
+          <a:gsLst>
+            <a:gs pos="0">
+              <a:schemeClr val="phClr">
+                <a:satMod val="300000"/>
+              </a:schemeClr>
+            </a:gs>
+            <a:gs pos="100000">
+              <a:schemeClr val="phClr">
+                <a:tint val="80000"/>
+                <a:satMod val="200000"/>
+              </a:schemeClr>
+            </a:gs>
+          </a:gsLst>
+          <a:path path="circle">
+            <a:fillToRect l="50000" t="50000" r="50000" b="50000"/>
+          </a:path>
         </a:gradFill>
       </a:bgFillStyleLst>
     </a:fmtScheme>
   </a:themeElements>
+  <a:objectDefaults/>
+  <a:extraClrSchemeLst/>
 </a:theme>
 </file>
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mx="http://schemas.microsoft.com/office/mac/excel/2008/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:mv="urn:schemas-microsoft-com:mac:vml" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xm="http://schemas.microsoft.com/office/excel/2006/main">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
   <sheetPr>
-    <outlinePr summaryBelow="0" summaryRight="0"/>
+    <outlinePr summaryBelow="0"/>
   </sheetPr>
-  <sheetFormatPr customHeight="1" defaultColWidth="12.63" defaultRowHeight="15.75"/>
+  <dimension ref="A1:F92"/>
+  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
-    <col customWidth="1" min="1" max="1" width="10.38"/>
-    <col customWidth="1" min="2" max="2" width="21.75"/>
-    <col customWidth="1" min="3" max="3" width="22.88"/>
-    <col customWidth="1" min="4" max="4" width="27.88"/>
-    <col customWidth="1" min="5" max="5" width="17.0"/>
-    <col customWidth="1" min="6" max="6" width="78.5"/>
+    <col min="1" max="1" style="5" width="10.43357142857143" customWidth="1" bestFit="1"/>
+    <col min="2" max="2" style="6" width="21.719285714285714" customWidth="1" bestFit="1"/>
+    <col min="3" max="3" style="7" width="22.862142857142857" customWidth="1" bestFit="1"/>
+    <col min="4" max="4" style="8" width="27.862142857142857" customWidth="1" bestFit="1"/>
+    <col min="5" max="5" style="7" width="64.14785714285713" customWidth="1" bestFit="1"/>
+    <col min="6" max="6" style="6" width="78.57642857142856" customWidth="1" bestFit="1"/>
   </cols>
   <sheetData>
-    <row r="1" ht="22.5" customHeight="1">
+    <row x14ac:dyDescent="0.25" r="1" customHeight="1" ht="22.5">
       <c r="A1" s="1" t="s">
         <v>0</v>
       </c>
@@ -2358,1562 +2383,1558 @@
       <c r="E1" s="3" t="s">
         <v>4</v>
       </c>
-      <c r="F1" s="4" t="s">
+      <c r="F1" s="2" t="s">
         <v>5</v>
       </c>
     </row>
-    <row r="2" ht="15.75" customHeight="1">
-      <c r="A2" s="5" t="s">
+    <row x14ac:dyDescent="0.25" r="2" customHeight="1" ht="438">
+      <c r="A2" s="1" t="s">
         <v>6</v>
       </c>
-      <c r="B2" s="6" t="s">
+      <c r="B2" s="2" t="s">
         <v>7</v>
       </c>
-      <c r="C2" s="7" t="s">
+      <c r="C2" s="3" t="s">
         <v>8</v>
       </c>
-      <c r="D2" s="8"/>
-      <c r="E2" s="7" t="s">
+      <c r="D2" s="4"/>
+      <c r="E2" s="3" t="s">
         <v>9</v>
       </c>
-      <c r="F2" s="9"/>
-    </row>
-    <row r="3" ht="15.75" customHeight="1">
-      <c r="A3" s="5" t="s">
+      <c r="F2" s="2"/>
+    </row>
+    <row x14ac:dyDescent="0.25" r="3" customHeight="1" ht="90">
+      <c r="A3" s="1" t="s">
         <v>10</v>
       </c>
-      <c r="B3" s="6" t="s">
+      <c r="B3" s="2" t="s">
         <v>11</v>
       </c>
-      <c r="C3" s="10" t="s">
+      <c r="C3" s="3" t="s">
         <v>12</v>
       </c>
-      <c r="D3" s="8" t="s">
+      <c r="D3" s="3" t="s">
         <v>13</v>
       </c>
-      <c r="E3" s="7" t="s">
+      <c r="E3" s="3" t="s">
         <v>14</v>
       </c>
-      <c r="F3" s="9"/>
-    </row>
-    <row r="4" ht="15.75" customHeight="1">
-      <c r="A4" s="5" t="s">
+      <c r="F3" s="2"/>
+    </row>
+    <row x14ac:dyDescent="0.25" r="4" customHeight="1" ht="90">
+      <c r="A4" s="1" t="s">
         <v>15</v>
       </c>
-      <c r="B4" s="6" t="s">
+      <c r="B4" s="2" t="s">
         <v>11</v>
       </c>
-      <c r="C4" s="10" t="s">
+      <c r="C4" s="3" t="s">
         <v>16</v>
       </c>
-      <c r="D4" s="8" t="s">
+      <c r="D4" s="3" t="s">
         <v>17</v>
       </c>
-      <c r="E4" s="7" t="s">
+      <c r="E4" s="3" t="s">
         <v>18</v>
       </c>
-      <c r="F4" s="9"/>
-    </row>
-    <row r="5" ht="15.75" customHeight="1">
-      <c r="A5" s="5" t="s">
+      <c r="F4" s="2"/>
+    </row>
+    <row x14ac:dyDescent="0.25" r="5" customHeight="1" ht="90">
+      <c r="A5" s="1" t="s">
         <v>19</v>
       </c>
-      <c r="B5" s="6" t="s">
+      <c r="B5" s="2" t="s">
         <v>11</v>
       </c>
-      <c r="C5" s="10" t="s">
+      <c r="C5" s="3" t="s">
         <v>20</v>
       </c>
-      <c r="D5" s="8" t="s">
+      <c r="D5" s="3" t="s">
         <v>21</v>
       </c>
-      <c r="E5" s="7" t="s">
+      <c r="E5" s="3" t="s">
         <v>22</v>
       </c>
-      <c r="F5" s="11"/>
-    </row>
-    <row r="6" ht="15.75" customHeight="1">
-      <c r="A6" s="5" t="s">
+      <c r="F5" s="2"/>
+    </row>
+    <row x14ac:dyDescent="0.25" r="6" customHeight="1" ht="90">
+      <c r="A6" s="1" t="s">
         <v>23</v>
       </c>
-      <c r="B6" s="6" t="s">
+      <c r="B6" s="2" t="s">
         <v>24</v>
       </c>
-      <c r="C6" s="10" t="s">
+      <c r="C6" s="3" t="s">
         <v>25</v>
       </c>
-      <c r="D6" s="8" t="s">
+      <c r="D6" s="3" t="s">
         <v>26</v>
       </c>
-      <c r="E6" s="7" t="s">
+      <c r="E6" s="3" t="s">
         <v>27</v>
       </c>
-      <c r="F6" s="11"/>
-    </row>
-    <row r="7" ht="15.75" customHeight="1">
-      <c r="A7" s="5" t="s">
+      <c r="F6" s="2"/>
+    </row>
+    <row x14ac:dyDescent="0.25" r="7" customHeight="1" ht="78">
+      <c r="A7" s="1" t="s">
         <v>28</v>
       </c>
-      <c r="B7" s="6" t="s">
+      <c r="B7" s="2" t="s">
         <v>24</v>
       </c>
-      <c r="C7" s="10" t="s">
+      <c r="C7" s="3" t="s">
         <v>29</v>
       </c>
-      <c r="D7" s="8" t="s">
+      <c r="D7" s="3" t="s">
         <v>30</v>
       </c>
-      <c r="E7" s="7" t="s">
+      <c r="E7" s="3" t="s">
         <v>31</v>
       </c>
-      <c r="F7" s="11"/>
-    </row>
-    <row r="8" ht="15.75" customHeight="1">
-      <c r="A8" s="5" t="s">
+      <c r="F7" s="2"/>
+    </row>
+    <row x14ac:dyDescent="0.25" r="8" customHeight="1" ht="90">
+      <c r="A8" s="1" t="s">
         <v>32</v>
       </c>
-      <c r="B8" s="6" t="s">
+      <c r="B8" s="2" t="s">
         <v>24</v>
       </c>
-      <c r="C8" s="10" t="s">
+      <c r="C8" s="3" t="s">
         <v>33</v>
       </c>
-      <c r="D8" s="8" t="s">
+      <c r="D8" s="3" t="s">
         <v>34</v>
       </c>
-      <c r="E8" s="7" t="s">
+      <c r="E8" s="3" t="s">
         <v>35</v>
       </c>
-      <c r="F8" s="11"/>
-    </row>
-    <row r="9" ht="15.75" customHeight="1">
-      <c r="A9" s="5" t="s">
+      <c r="F8" s="2"/>
+    </row>
+    <row x14ac:dyDescent="0.25" r="9" customHeight="1" ht="78">
+      <c r="A9" s="1" t="s">
         <v>36</v>
       </c>
-      <c r="B9" s="6" t="s">
+      <c r="B9" s="2" t="s">
         <v>24</v>
       </c>
-      <c r="C9" s="10" t="s">
+      <c r="C9" s="3" t="s">
         <v>37</v>
       </c>
-      <c r="D9" s="8" t="s">
+      <c r="D9" s="3" t="s">
         <v>38</v>
       </c>
-      <c r="E9" s="7" t="s">
+      <c r="E9" s="3" t="s">
         <v>39</v>
       </c>
-      <c r="F9" s="9"/>
-    </row>
-    <row r="10" ht="15.75" customHeight="1">
-      <c r="A10" s="5" t="s">
+      <c r="F9" s="2"/>
+    </row>
+    <row x14ac:dyDescent="0.25" r="10" customHeight="1" ht="246">
+      <c r="A10" s="1" t="s">
         <v>40</v>
       </c>
-      <c r="B10" s="6" t="s">
+      <c r="B10" s="2" t="s">
         <v>41</v>
       </c>
-      <c r="C10" s="10" t="s">
+      <c r="C10" s="3" t="s">
         <v>42</v>
       </c>
-      <c r="D10" s="8"/>
-      <c r="E10" s="7" t="s">
+      <c r="D10" s="4"/>
+      <c r="E10" s="3" t="s">
         <v>43</v>
       </c>
-      <c r="F10" s="9"/>
-    </row>
-    <row r="11" ht="15.75" customHeight="1">
-      <c r="A11" s="5" t="s">
+      <c r="F10" s="2"/>
+    </row>
+    <row x14ac:dyDescent="0.25" r="11" customHeight="1" ht="102">
+      <c r="A11" s="1" t="s">
         <v>44</v>
       </c>
-      <c r="B11" s="6" t="s">
+      <c r="B11" s="2" t="s">
         <v>45</v>
       </c>
-      <c r="C11" s="10" t="s">
+      <c r="C11" s="3" t="s">
         <v>46</v>
       </c>
-      <c r="D11" s="8" t="s">
+      <c r="D11" s="3" t="s">
         <v>47</v>
       </c>
-      <c r="E11" s="7" t="s">
+      <c r="E11" s="3" t="s">
         <v>48</v>
       </c>
-      <c r="F11" s="9"/>
-    </row>
-    <row r="12" ht="15.75" customHeight="1">
-      <c r="A12" s="5" t="s">
+      <c r="F11" s="2"/>
+    </row>
+    <row x14ac:dyDescent="0.25" r="12" customHeight="1" ht="126">
+      <c r="A12" s="1" t="s">
         <v>49</v>
       </c>
-      <c r="B12" s="6" t="s">
+      <c r="B12" s="2" t="s">
         <v>50</v>
       </c>
-      <c r="C12" s="10" t="s">
+      <c r="C12" s="3" t="s">
         <v>51</v>
       </c>
-      <c r="D12" s="8" t="s">
+      <c r="D12" s="3" t="s">
         <v>52</v>
       </c>
-      <c r="E12" s="7" t="s">
+      <c r="E12" s="3" t="s">
         <v>53</v>
       </c>
-      <c r="F12" s="9"/>
-    </row>
-    <row r="13" ht="15.75" customHeight="1">
-      <c r="A13" s="5" t="s">
+      <c r="F12" s="2"/>
+    </row>
+    <row x14ac:dyDescent="0.25" r="13" customHeight="1" ht="246">
+      <c r="A13" s="1" t="s">
         <v>54</v>
       </c>
-      <c r="B13" s="6" t="s">
+      <c r="B13" s="2" t="s">
         <v>41</v>
       </c>
-      <c r="C13" s="10" t="s">
+      <c r="C13" s="3" t="s">
         <v>55</v>
       </c>
-      <c r="D13" s="8"/>
-      <c r="E13" s="7" t="s">
+      <c r="D13" s="4"/>
+      <c r="E13" s="3" t="s">
         <v>56</v>
       </c>
-      <c r="F13" s="9"/>
-    </row>
-    <row r="14" ht="15.75" customHeight="1">
-      <c r="A14" s="5" t="s">
+      <c r="F13" s="2"/>
+    </row>
+    <row x14ac:dyDescent="0.25" r="14" customHeight="1" ht="246">
+      <c r="A14" s="1" t="s">
         <v>57</v>
       </c>
-      <c r="B14" s="6" t="s">
+      <c r="B14" s="2" t="s">
         <v>41</v>
       </c>
-      <c r="C14" s="7" t="s">
+      <c r="C14" s="3" t="s">
         <v>58</v>
       </c>
-      <c r="D14" s="12"/>
-      <c r="E14" s="7" t="s">
+      <c r="D14" s="4"/>
+      <c r="E14" s="3" t="s">
         <v>59</v>
       </c>
-      <c r="F14" s="11"/>
-    </row>
-    <row r="15" ht="15.75" customHeight="1">
-      <c r="A15" s="5" t="s">
+      <c r="F14" s="2"/>
+    </row>
+    <row x14ac:dyDescent="0.25" r="15" customHeight="1" ht="258">
+      <c r="A15" s="1" t="s">
         <v>60</v>
       </c>
-      <c r="B15" s="6" t="s">
+      <c r="B15" s="2" t="s">
         <v>41</v>
       </c>
-      <c r="C15" s="7" t="s">
+      <c r="C15" s="3" t="s">
         <v>61</v>
       </c>
-      <c r="D15" s="12"/>
-      <c r="E15" s="7" t="s">
+      <c r="D15" s="4"/>
+      <c r="E15" s="3" t="s">
         <v>62</v>
       </c>
-      <c r="F15" s="11"/>
-    </row>
-    <row r="16" ht="15.75" customHeight="1">
-      <c r="A16" s="5" t="s">
+      <c r="F15" s="2"/>
+    </row>
+    <row x14ac:dyDescent="0.25" r="16" customHeight="1" ht="246">
+      <c r="A16" s="1" t="s">
         <v>63</v>
       </c>
-      <c r="B16" s="6" t="s">
+      <c r="B16" s="2" t="s">
         <v>41</v>
       </c>
-      <c r="C16" s="7" t="s">
+      <c r="C16" s="3" t="s">
         <v>64</v>
       </c>
-      <c r="D16" s="13"/>
-      <c r="E16" s="7" t="s">
+      <c r="D16" s="4"/>
+      <c r="E16" s="3" t="s">
         <v>65</v>
       </c>
-      <c r="F16" s="11"/>
-    </row>
-    <row r="17" ht="15.75" customHeight="1">
-      <c r="A17" s="5" t="s">
+      <c r="F16" s="2"/>
+    </row>
+    <row x14ac:dyDescent="0.25" r="17" customHeight="1" ht="258">
+      <c r="A17" s="1" t="s">
         <v>66</v>
       </c>
-      <c r="B17" s="6" t="s">
+      <c r="B17" s="2" t="s">
         <v>41</v>
       </c>
-      <c r="C17" s="10" t="s">
+      <c r="C17" s="3" t="s">
         <v>67</v>
       </c>
-      <c r="D17" s="14"/>
-      <c r="E17" s="7" t="s">
+      <c r="D17" s="4"/>
+      <c r="E17" s="3" t="s">
         <v>68</v>
       </c>
-      <c r="F17" s="9"/>
-    </row>
-    <row r="18" ht="15.75" customHeight="1">
-      <c r="A18" s="5" t="s">
+      <c r="F17" s="2"/>
+    </row>
+    <row x14ac:dyDescent="0.25" r="18" customHeight="1" ht="90">
+      <c r="A18" s="1" t="s">
         <v>69</v>
       </c>
-      <c r="B18" s="6" t="s">
+      <c r="B18" s="2" t="s">
         <v>45</v>
       </c>
-      <c r="C18" s="7" t="s">
+      <c r="C18" s="3" t="s">
         <v>70</v>
       </c>
-      <c r="D18" s="12"/>
-      <c r="E18" s="7" t="s">
+      <c r="D18" s="4"/>
+      <c r="E18" s="3" t="s">
         <v>71</v>
       </c>
-      <c r="F18" s="11"/>
-    </row>
-    <row r="19" ht="15.75" customHeight="1">
-      <c r="A19" s="5" t="s">
+      <c r="F18" s="2"/>
+    </row>
+    <row x14ac:dyDescent="0.25" r="19" customHeight="1" ht="90">
+      <c r="A19" s="1" t="s">
         <v>72</v>
       </c>
-      <c r="B19" s="6" t="s">
+      <c r="B19" s="2" t="s">
         <v>45</v>
       </c>
-      <c r="C19" s="7" t="s">
+      <c r="C19" s="3" t="s">
         <v>73</v>
       </c>
-      <c r="D19" s="12"/>
-      <c r="E19" s="7" t="s">
+      <c r="D19" s="4"/>
+      <c r="E19" s="3" t="s">
         <v>74</v>
       </c>
-      <c r="F19" s="11"/>
-    </row>
-    <row r="20" ht="15.75" customHeight="1">
-      <c r="A20" s="5" t="s">
+      <c r="F19" s="2"/>
+    </row>
+    <row x14ac:dyDescent="0.25" r="20" customHeight="1" ht="90">
+      <c r="A20" s="1" t="s">
         <v>75</v>
       </c>
-      <c r="B20" s="6" t="s">
+      <c r="B20" s="2" t="s">
         <v>45</v>
       </c>
-      <c r="C20" s="7" t="s">
+      <c r="C20" s="3" t="s">
         <v>76</v>
       </c>
-      <c r="D20" s="13"/>
-      <c r="E20" s="7" t="s">
+      <c r="D20" s="4"/>
+      <c r="E20" s="3" t="s">
         <v>77</v>
       </c>
-      <c r="F20" s="11"/>
-    </row>
-    <row r="21" ht="15.75" customHeight="1">
-      <c r="A21" s="5" t="s">
+      <c r="F20" s="2"/>
+    </row>
+    <row x14ac:dyDescent="0.25" r="21" customHeight="1" ht="90">
+      <c r="A21" s="1" t="s">
         <v>78</v>
       </c>
-      <c r="B21" s="6" t="s">
+      <c r="B21" s="2" t="s">
         <v>79</v>
       </c>
-      <c r="C21" s="7" t="s">
+      <c r="C21" s="3" t="s">
         <v>80</v>
       </c>
-      <c r="D21" s="12"/>
-      <c r="E21" s="7" t="s">
+      <c r="D21" s="4"/>
+      <c r="E21" s="3" t="s">
         <v>81</v>
       </c>
-      <c r="F21" s="11"/>
-    </row>
-    <row r="22" ht="15.75" customHeight="1">
-      <c r="A22" s="5" t="s">
+      <c r="F21" s="2"/>
+    </row>
+    <row x14ac:dyDescent="0.25" r="22" customHeight="1" ht="90">
+      <c r="A22" s="1" t="s">
         <v>82</v>
       </c>
-      <c r="B22" s="6" t="s">
+      <c r="B22" s="2" t="s">
         <v>79</v>
       </c>
-      <c r="C22" s="7" t="s">
+      <c r="C22" s="3" t="s">
         <v>83</v>
       </c>
-      <c r="D22" s="12"/>
-      <c r="E22" s="7" t="s">
+      <c r="D22" s="4"/>
+      <c r="E22" s="3" t="s">
         <v>84</v>
       </c>
-      <c r="F22" s="11"/>
-    </row>
-    <row r="23" ht="15.75" customHeight="1">
-      <c r="A23" s="5" t="s">
+      <c r="F22" s="2"/>
+    </row>
+    <row x14ac:dyDescent="0.25" r="23" customHeight="1" ht="90">
+      <c r="A23" s="1" t="s">
         <v>85</v>
       </c>
-      <c r="B23" s="6" t="s">
+      <c r="B23" s="2" t="s">
         <v>79</v>
       </c>
-      <c r="C23" s="7" t="s">
+      <c r="C23" s="3" t="s">
         <v>86</v>
       </c>
-      <c r="D23" s="12"/>
-      <c r="E23" s="7" t="s">
+      <c r="D23" s="4"/>
+      <c r="E23" s="3" t="s">
         <v>87</v>
       </c>
-      <c r="F23" s="11"/>
-    </row>
-    <row r="24" ht="15.75" customHeight="1">
-      <c r="A24" s="5" t="s">
+      <c r="F23" s="2"/>
+    </row>
+    <row x14ac:dyDescent="0.25" r="24" customHeight="1" ht="95.25">
+      <c r="A24" s="1" t="s">
         <v>88</v>
       </c>
-      <c r="B24" s="6" t="s">
+      <c r="B24" s="2" t="s">
         <v>79</v>
       </c>
-      <c r="C24" s="7" t="s">
+      <c r="C24" s="3" t="s">
         <v>89</v>
       </c>
-      <c r="D24" s="12"/>
-      <c r="E24" s="7" t="s">
+      <c r="D24" s="4"/>
+      <c r="E24" s="3" t="s">
         <v>90</v>
       </c>
-      <c r="F24" s="11"/>
-    </row>
-    <row r="25" ht="15.75" customHeight="1">
-      <c r="A25" s="5" t="s">
+      <c r="F24" s="2"/>
+    </row>
+    <row x14ac:dyDescent="0.25" r="25" customHeight="1" ht="95.25">
+      <c r="A25" s="1" t="s">
         <v>91</v>
       </c>
-      <c r="B25" s="6" t="s">
+      <c r="B25" s="2" t="s">
         <v>79</v>
       </c>
-      <c r="C25" s="10" t="s">
+      <c r="C25" s="3" t="s">
         <v>92</v>
       </c>
-      <c r="D25" s="8"/>
-      <c r="E25" s="7" t="s">
+      <c r="D25" s="4"/>
+      <c r="E25" s="3" t="s">
         <v>93</v>
       </c>
-      <c r="F25" s="11"/>
-    </row>
-    <row r="26" ht="15.75" customHeight="1">
-      <c r="A26" s="5" t="s">
+      <c r="F25" s="2"/>
+    </row>
+    <row x14ac:dyDescent="0.25" r="26" customHeight="1" ht="95.25">
+      <c r="A26" s="1" t="s">
         <v>94</v>
       </c>
-      <c r="B26" s="6" t="s">
+      <c r="B26" s="2" t="s">
         <v>79</v>
       </c>
-      <c r="C26" s="10" t="s">
+      <c r="C26" s="3" t="s">
         <v>95</v>
       </c>
-      <c r="D26" s="8"/>
-      <c r="E26" s="7" t="s">
+      <c r="D26" s="4"/>
+      <c r="E26" s="3" t="s">
         <v>96</v>
       </c>
-      <c r="F26" s="11"/>
-    </row>
-    <row r="27" ht="15.75" customHeight="1">
-      <c r="A27" s="5" t="s">
+      <c r="F26" s="2"/>
+    </row>
+    <row x14ac:dyDescent="0.25" r="27" customHeight="1" ht="95.25">
+      <c r="A27" s="1" t="s">
         <v>97</v>
       </c>
-      <c r="B27" s="6" t="s">
+      <c r="B27" s="2" t="s">
         <v>79</v>
       </c>
-      <c r="C27" s="10" t="s">
+      <c r="C27" s="3" t="s">
         <v>98</v>
       </c>
-      <c r="D27" s="8"/>
-      <c r="E27" s="7" t="s">
+      <c r="D27" s="4"/>
+      <c r="E27" s="3" t="s">
         <v>99</v>
       </c>
-      <c r="F27" s="11"/>
-    </row>
-    <row r="28" ht="15.75" customHeight="1">
-      <c r="A28" s="5" t="s">
+      <c r="F27" s="2"/>
+    </row>
+    <row x14ac:dyDescent="0.25" r="28" customHeight="1" ht="95.25">
+      <c r="A28" s="1" t="s">
         <v>100</v>
       </c>
-      <c r="B28" s="6" t="s">
+      <c r="B28" s="2" t="s">
         <v>79</v>
       </c>
-      <c r="C28" s="10" t="s">
+      <c r="C28" s="3" t="s">
         <v>101</v>
       </c>
-      <c r="D28" s="8"/>
-      <c r="E28" s="7" t="s">
+      <c r="D28" s="4"/>
+      <c r="E28" s="3" t="s">
         <v>102</v>
       </c>
-      <c r="F28" s="9"/>
-    </row>
-    <row r="29" ht="15.75" customHeight="1">
-      <c r="A29" s="5" t="s">
+      <c r="F28" s="2"/>
+    </row>
+    <row x14ac:dyDescent="0.25" r="29" customHeight="1" ht="95.25">
+      <c r="A29" s="1" t="s">
         <v>103</v>
       </c>
-      <c r="B29" s="6" t="s">
+      <c r="B29" s="2" t="s">
         <v>45</v>
       </c>
-      <c r="C29" s="10" t="s">
+      <c r="C29" s="3" t="s">
         <v>104</v>
       </c>
-      <c r="D29" s="14"/>
-      <c r="E29" s="7" t="s">
+      <c r="D29" s="4"/>
+      <c r="E29" s="3" t="s">
         <v>105</v>
       </c>
-      <c r="F29" s="11"/>
-    </row>
-    <row r="30" ht="15.75" customHeight="1">
-      <c r="A30" s="5" t="s">
+      <c r="F29" s="2"/>
+    </row>
+    <row x14ac:dyDescent="0.25" r="30" customHeight="1" ht="567">
+      <c r="A30" s="1" t="s">
         <v>106</v>
       </c>
-      <c r="B30" s="6" t="s">
+      <c r="B30" s="2" t="s">
         <v>7</v>
       </c>
-      <c r="C30" s="10" t="s">
+      <c r="C30" s="3" t="s">
         <v>107</v>
       </c>
-      <c r="D30" s="14"/>
-      <c r="E30" s="7" t="s">
+      <c r="D30" s="4"/>
+      <c r="E30" s="3" t="s">
         <v>108</v>
       </c>
-      <c r="F30" s="11"/>
-    </row>
-    <row r="31" ht="15.75" customHeight="1">
-      <c r="A31" s="5" t="s">
+      <c r="F30" s="2"/>
+    </row>
+    <row x14ac:dyDescent="0.25" r="31" customHeight="1" ht="95.25">
+      <c r="A31" s="1" t="s">
         <v>109</v>
       </c>
-      <c r="B31" s="6" t="s">
+      <c r="B31" s="2" t="s">
         <v>11</v>
       </c>
-      <c r="C31" s="10" t="s">
+      <c r="C31" s="3" t="s">
         <v>110</v>
       </c>
-      <c r="D31" s="8" t="s">
+      <c r="D31" s="3" t="s">
         <v>13</v>
       </c>
-      <c r="E31" s="7" t="s">
+      <c r="E31" s="3" t="s">
         <v>111</v>
       </c>
-      <c r="F31" s="11"/>
-    </row>
-    <row r="32" ht="15.75" customHeight="1">
-      <c r="A32" s="5" t="s">
+      <c r="F31" s="2"/>
+    </row>
+    <row x14ac:dyDescent="0.25" r="32" customHeight="1" ht="95.25">
+      <c r="A32" s="1" t="s">
         <v>112</v>
       </c>
-      <c r="B32" s="6" t="s">
+      <c r="B32" s="2" t="s">
         <v>11</v>
       </c>
-      <c r="C32" s="10" t="s">
+      <c r="C32" s="3" t="s">
         <v>113</v>
       </c>
-      <c r="D32" s="8" t="s">
+      <c r="D32" s="3" t="s">
         <v>17</v>
       </c>
-      <c r="E32" s="7" t="s">
+      <c r="E32" s="3" t="s">
         <v>114</v>
       </c>
-      <c r="F32" s="11"/>
-    </row>
-    <row r="33" ht="15.75" customHeight="1">
-      <c r="A33" s="5" t="s">
+      <c r="F32" s="2"/>
+    </row>
+    <row x14ac:dyDescent="0.25" r="33" customHeight="1" ht="82.5">
+      <c r="A33" s="1" t="s">
         <v>115</v>
       </c>
-      <c r="B33" s="6" t="s">
+      <c r="B33" s="2" t="s">
         <v>24</v>
       </c>
-      <c r="C33" s="7" t="s">
+      <c r="C33" s="3" t="s">
         <v>116</v>
       </c>
-      <c r="D33" s="8" t="s">
+      <c r="D33" s="3" t="s">
         <v>26</v>
       </c>
-      <c r="E33" s="7" t="s">
+      <c r="E33" s="3" t="s">
         <v>117</v>
       </c>
-      <c r="F33" s="9"/>
-    </row>
-    <row r="34" ht="15.75" customHeight="1">
-      <c r="A34" s="5" t="s">
+      <c r="F33" s="2"/>
+    </row>
+    <row x14ac:dyDescent="0.25" r="34" customHeight="1" ht="15.75">
+      <c r="A34" s="1" t="s">
         <v>118</v>
       </c>
-      <c r="B34" s="6" t="s">
+      <c r="B34" s="2" t="s">
         <v>79</v>
       </c>
-      <c r="C34" s="7" t="s">
+      <c r="C34" s="3" t="s">
         <v>119</v>
       </c>
-      <c r="D34" s="14"/>
-      <c r="E34" s="7" t="s">
+      <c r="D34" s="4"/>
+      <c r="E34" s="3" t="s">
         <v>120</v>
       </c>
-      <c r="F34" s="11" t="s">
+      <c r="F34" s="2" t="s">
         <v>121</v>
       </c>
     </row>
-    <row r="35" ht="15.75" customHeight="1">
-      <c r="A35" s="5" t="s">
+    <row x14ac:dyDescent="0.25" r="35" customHeight="1" ht="15.75">
+      <c r="A35" s="1" t="s">
         <v>122</v>
       </c>
-      <c r="B35" s="6" t="s">
+      <c r="B35" s="2" t="s">
         <v>45</v>
       </c>
-      <c r="C35" s="7" t="s">
+      <c r="C35" s="3" t="s">
         <v>46</v>
       </c>
-      <c r="D35" s="8" t="s">
+      <c r="D35" s="3" t="s">
         <v>123</v>
       </c>
-      <c r="E35" s="7" t="s">
+      <c r="E35" s="3" t="s">
         <v>124</v>
       </c>
-      <c r="F35" s="11"/>
-    </row>
-    <row r="36" ht="15.75" customHeight="1">
-      <c r="A36" s="5" t="s">
+      <c r="F35" s="2"/>
+    </row>
+    <row x14ac:dyDescent="0.25" r="36" customHeight="1" ht="15.75">
+      <c r="A36" s="1" t="s">
         <v>125</v>
       </c>
-      <c r="B36" s="6" t="s">
+      <c r="B36" s="2" t="s">
         <v>45</v>
       </c>
-      <c r="C36" s="10" t="s">
+      <c r="C36" s="3" t="s">
         <v>126</v>
       </c>
-      <c r="D36" s="8" t="s">
+      <c r="D36" s="3" t="s">
         <v>127</v>
       </c>
-      <c r="E36" s="7" t="s">
+      <c r="E36" s="3" t="s">
         <v>128</v>
       </c>
-      <c r="F36" s="9"/>
-    </row>
-    <row r="37" ht="15.75" customHeight="1">
-      <c r="A37" s="5" t="s">
+      <c r="F36" s="2"/>
+    </row>
+    <row x14ac:dyDescent="0.25" r="37" customHeight="1" ht="15.75">
+      <c r="A37" s="1" t="s">
         <v>129</v>
       </c>
-      <c r="B37" s="6" t="s">
+      <c r="B37" s="2" t="s">
         <v>45</v>
       </c>
-      <c r="C37" s="10" t="s">
+      <c r="C37" s="3" t="s">
         <v>130</v>
       </c>
-      <c r="D37" s="8" t="s">
+      <c r="D37" s="3" t="s">
         <v>131</v>
       </c>
-      <c r="E37" s="7" t="s">
+      <c r="E37" s="3" t="s">
         <v>132</v>
       </c>
-      <c r="F37" s="11"/>
-    </row>
-    <row r="38" ht="15.75" customHeight="1">
-      <c r="A38" s="5" t="s">
+      <c r="F37" s="2"/>
+    </row>
+    <row x14ac:dyDescent="0.25" r="38" customHeight="1" ht="15.75">
+      <c r="A38" s="1" t="s">
         <v>133</v>
       </c>
-      <c r="B38" s="6" t="s">
+      <c r="B38" s="2" t="s">
         <v>45</v>
       </c>
-      <c r="C38" s="7" t="s">
+      <c r="C38" s="3" t="s">
         <v>134</v>
       </c>
-      <c r="D38" s="8" t="s">
+      <c r="D38" s="3" t="s">
         <v>135</v>
       </c>
-      <c r="E38" s="7" t="s">
+      <c r="E38" s="3" t="s">
         <v>136</v>
       </c>
-      <c r="F38" s="9"/>
-    </row>
-    <row r="39" ht="15.75" customHeight="1">
-      <c r="A39" s="5" t="s">
+      <c r="F38" s="2"/>
+    </row>
+    <row x14ac:dyDescent="0.25" r="39" customHeight="1" ht="15.75">
+      <c r="A39" s="1" t="s">
         <v>137</v>
       </c>
-      <c r="B39" s="6" t="s">
+      <c r="B39" s="2" t="s">
         <v>45</v>
       </c>
-      <c r="C39" s="7" t="s">
+      <c r="C39" s="3" t="s">
         <v>138</v>
       </c>
-      <c r="D39" s="8" t="s">
+      <c r="D39" s="3" t="s">
         <v>139</v>
       </c>
-      <c r="E39" s="7" t="s">
+      <c r="E39" s="3" t="s">
         <v>140</v>
       </c>
-      <c r="F39" s="9"/>
-    </row>
-    <row r="40" ht="15.75" customHeight="1">
-      <c r="A40" s="5" t="s">
+      <c r="F39" s="2"/>
+    </row>
+    <row x14ac:dyDescent="0.25" r="40" customHeight="1" ht="15.75">
+      <c r="A40" s="1" t="s">
         <v>141</v>
       </c>
-      <c r="B40" s="6" t="s">
+      <c r="B40" s="2" t="s">
         <v>45</v>
       </c>
-      <c r="C40" s="10" t="s">
+      <c r="C40" s="3" t="s">
         <v>142</v>
       </c>
-      <c r="D40" s="8" t="s">
+      <c r="D40" s="3" t="s">
         <v>143</v>
       </c>
-      <c r="E40" s="7" t="s">
+      <c r="E40" s="3" t="s">
         <v>144</v>
       </c>
-      <c r="F40" s="9"/>
-    </row>
-    <row r="41" ht="15.75" customHeight="1">
-      <c r="A41" s="5" t="s">
+      <c r="F40" s="2"/>
+    </row>
+    <row x14ac:dyDescent="0.25" r="41" customHeight="1" ht="15.75">
+      <c r="A41" s="1" t="s">
         <v>145</v>
       </c>
-      <c r="B41" s="6" t="s">
+      <c r="B41" s="2" t="s">
         <v>45</v>
       </c>
-      <c r="C41" s="10" t="s">
+      <c r="C41" s="3" t="s">
         <v>146</v>
       </c>
-      <c r="D41" s="8" t="s">
+      <c r="D41" s="3" t="s">
         <v>147</v>
       </c>
-      <c r="E41" s="7" t="s">
+      <c r="E41" s="3" t="s">
         <v>148</v>
       </c>
-      <c r="F41" s="9"/>
-    </row>
-    <row r="42" ht="15.75" customHeight="1">
-      <c r="A42" s="5" t="s">
+      <c r="F41" s="2"/>
+    </row>
+    <row x14ac:dyDescent="0.25" r="42" customHeight="1" ht="15.75">
+      <c r="A42" s="1" t="s">
         <v>149</v>
       </c>
-      <c r="B42" s="6" t="s">
+      <c r="B42" s="2" t="s">
         <v>41</v>
       </c>
-      <c r="C42" s="7" t="s">
+      <c r="C42" s="3" t="s">
         <v>150</v>
       </c>
-      <c r="D42" s="8" t="s">
+      <c r="D42" s="3" t="s">
         <v>151</v>
       </c>
-      <c r="E42" s="7" t="s">
+      <c r="E42" s="3" t="s">
         <v>152</v>
       </c>
-      <c r="F42" s="9"/>
-    </row>
-    <row r="43" ht="15.75" customHeight="1">
-      <c r="A43" s="5" t="s">
+      <c r="F42" s="2"/>
+    </row>
+    <row x14ac:dyDescent="0.25" r="43" customHeight="1" ht="15.75">
+      <c r="A43" s="1" t="s">
         <v>153</v>
       </c>
-      <c r="B43" s="6" t="s">
+      <c r="B43" s="2" t="s">
         <v>41</v>
       </c>
-      <c r="C43" s="7" t="s">
+      <c r="C43" s="3" t="s">
         <v>150</v>
       </c>
-      <c r="D43" s="8" t="s">
+      <c r="D43" s="3" t="s">
         <v>154</v>
       </c>
-      <c r="E43" s="7" t="s">
+      <c r="E43" s="3" t="s">
         <v>155</v>
       </c>
-      <c r="F43" s="9"/>
-    </row>
-    <row r="44" ht="15.75" customHeight="1">
-      <c r="A44" s="5" t="s">
+      <c r="F43" s="2"/>
+    </row>
+    <row x14ac:dyDescent="0.25" r="44" customHeight="1" ht="15.75">
+      <c r="A44" s="1" t="s">
         <v>156</v>
       </c>
-      <c r="B44" s="6" t="s">
+      <c r="B44" s="2" t="s">
         <v>41</v>
       </c>
-      <c r="C44" s="10" t="s">
+      <c r="C44" s="3" t="s">
         <v>157</v>
       </c>
-      <c r="D44" s="8" t="s">
+      <c r="D44" s="3" t="s">
         <v>158</v>
       </c>
-      <c r="E44" s="7" t="s">
+      <c r="E44" s="3" t="s">
         <v>159</v>
       </c>
-      <c r="F44" s="9"/>
-    </row>
-    <row r="45" ht="15.75" customHeight="1">
-      <c r="A45" s="5" t="s">
+      <c r="F44" s="2"/>
+    </row>
+    <row x14ac:dyDescent="0.25" r="45" customHeight="1" ht="15.75">
+      <c r="A45" s="1" t="s">
         <v>160</v>
       </c>
-      <c r="B45" s="6" t="s">
+      <c r="B45" s="2" t="s">
         <v>41</v>
       </c>
-      <c r="C45" s="10" t="s">
+      <c r="C45" s="3" t="s">
         <v>157</v>
       </c>
-      <c r="D45" s="8" t="s">
+      <c r="D45" s="3" t="s">
         <v>161</v>
       </c>
-      <c r="E45" s="7" t="s">
+      <c r="E45" s="3" t="s">
         <v>162</v>
       </c>
-      <c r="F45" s="9"/>
-    </row>
-    <row r="46" ht="15.75" customHeight="1">
-      <c r="A46" s="5" t="s">
+      <c r="F45" s="2"/>
+    </row>
+    <row x14ac:dyDescent="0.25" r="46" customHeight="1" ht="15.75">
+      <c r="A46" s="1" t="s">
         <v>163</v>
       </c>
-      <c r="B46" s="6" t="s">
+      <c r="B46" s="2" t="s">
         <v>41</v>
       </c>
-      <c r="C46" s="7" t="s">
+      <c r="C46" s="3" t="s">
         <v>164</v>
       </c>
-      <c r="D46" s="14"/>
-      <c r="E46" s="7" t="s">
+      <c r="D46" s="4"/>
+      <c r="E46" s="3" t="s">
         <v>165</v>
       </c>
-      <c r="F46" s="11"/>
-    </row>
-    <row r="47" ht="15.75" customHeight="1">
-      <c r="A47" s="5" t="s">
+      <c r="F46" s="2"/>
+    </row>
+    <row x14ac:dyDescent="0.25" r="47" customHeight="1" ht="15.75">
+      <c r="A47" s="1" t="s">
         <v>166</v>
       </c>
-      <c r="B47" s="6" t="s">
+      <c r="B47" s="2" t="s">
         <v>41</v>
       </c>
-      <c r="C47" s="10" t="s">
+      <c r="C47" s="3" t="s">
         <v>167</v>
       </c>
-      <c r="D47" s="8"/>
-      <c r="E47" s="7" t="s">
+      <c r="D47" s="4"/>
+      <c r="E47" s="3" t="s">
         <v>168</v>
       </c>
-      <c r="F47" s="11"/>
-    </row>
-    <row r="48" ht="15.75" customHeight="1">
-      <c r="A48" s="5" t="s">
+      <c r="F47" s="2"/>
+    </row>
+    <row x14ac:dyDescent="0.25" r="48" customHeight="1" ht="15.75">
+      <c r="A48" s="1" t="s">
         <v>169</v>
       </c>
-      <c r="B48" s="6" t="s">
+      <c r="B48" s="2" t="s">
         <v>41</v>
       </c>
-      <c r="C48" s="10" t="s">
+      <c r="C48" s="3" t="s">
         <v>170</v>
       </c>
-      <c r="D48" s="8"/>
-      <c r="E48" s="7" t="s">
+      <c r="D48" s="4"/>
+      <c r="E48" s="3" t="s">
         <v>171</v>
       </c>
-      <c r="F48" s="11"/>
-    </row>
-    <row r="49" ht="15.75" customHeight="1">
-      <c r="A49" s="5" t="s">
+      <c r="F48" s="2"/>
+    </row>
+    <row x14ac:dyDescent="0.25" r="49" customHeight="1" ht="15.75">
+      <c r="A49" s="1" t="s">
         <v>172</v>
       </c>
-      <c r="B49" s="6" t="s">
+      <c r="B49" s="2" t="s">
         <v>41</v>
       </c>
-      <c r="C49" s="10" t="s">
+      <c r="C49" s="3" t="s">
         <v>173</v>
       </c>
-      <c r="D49" s="8"/>
-      <c r="E49" s="7" t="s">
+      <c r="D49" s="4"/>
+      <c r="E49" s="3" t="s">
         <v>174</v>
       </c>
-      <c r="F49" s="11"/>
-    </row>
-    <row r="50" ht="15.75" customHeight="1">
-      <c r="A50" s="5" t="s">
+      <c r="F49" s="2"/>
+    </row>
+    <row x14ac:dyDescent="0.25" r="50" customHeight="1" ht="246">
+      <c r="A50" s="1" t="s">
         <v>175</v>
       </c>
-      <c r="B50" s="6" t="s">
+      <c r="B50" s="2" t="s">
         <v>41</v>
       </c>
-      <c r="C50" s="10" t="s">
+      <c r="C50" s="3" t="s">
         <v>176</v>
       </c>
-      <c r="D50" s="8"/>
-      <c r="E50" s="7" t="s">
+      <c r="D50" s="4"/>
+      <c r="E50" s="3" t="s">
         <v>177</v>
       </c>
-      <c r="F50" s="11"/>
-    </row>
-    <row r="51" ht="15.75" customHeight="1">
-      <c r="A51" s="5" t="s">
+      <c r="F50" s="2"/>
+    </row>
+    <row x14ac:dyDescent="0.25" r="51" customHeight="1" ht="15.75">
+      <c r="A51" s="1" t="s">
         <v>178</v>
       </c>
-      <c r="B51" s="6" t="s">
+      <c r="B51" s="2" t="s">
         <v>41</v>
       </c>
-      <c r="C51" s="10" t="s">
+      <c r="C51" s="3" t="s">
         <v>179</v>
       </c>
-      <c r="D51" s="8"/>
-      <c r="E51" s="7" t="s">
+      <c r="D51" s="4"/>
+      <c r="E51" s="3" t="s">
         <v>180</v>
       </c>
-      <c r="F51" s="11"/>
-    </row>
-    <row r="52" ht="15.75" customHeight="1">
-      <c r="A52" s="5" t="s">
+      <c r="F51" s="2"/>
+    </row>
+    <row x14ac:dyDescent="0.25" r="52" customHeight="1" ht="15.75">
+      <c r="A52" s="1" t="s">
         <v>181</v>
       </c>
-      <c r="B52" s="6" t="s">
+      <c r="B52" s="2" t="s">
         <v>41</v>
       </c>
-      <c r="C52" s="10" t="s">
+      <c r="C52" s="3" t="s">
         <v>182</v>
       </c>
-      <c r="D52" s="8" t="s">
+      <c r="D52" s="3" t="s">
         <v>183</v>
       </c>
-      <c r="E52" s="7" t="s">
+      <c r="E52" s="3" t="s">
         <v>184</v>
       </c>
-      <c r="F52" s="11"/>
-    </row>
-    <row r="53" ht="15.75" customHeight="1">
-      <c r="A53" s="5" t="s">
+      <c r="F52" s="2"/>
+    </row>
+    <row x14ac:dyDescent="0.25" r="53" customHeight="1" ht="15.75">
+      <c r="A53" s="1" t="s">
         <v>185</v>
       </c>
-      <c r="B53" s="6" t="s">
+      <c r="B53" s="2" t="s">
         <v>41</v>
       </c>
-      <c r="C53" s="10" t="s">
+      <c r="C53" s="3" t="s">
         <v>182</v>
       </c>
-      <c r="D53" s="8" t="s">
+      <c r="D53" s="3" t="s">
         <v>186</v>
       </c>
-      <c r="E53" s="7" t="s">
+      <c r="E53" s="3" t="s">
         <v>187</v>
       </c>
-      <c r="F53" s="11"/>
-    </row>
-    <row r="54" ht="15.75" customHeight="1">
-      <c r="A54" s="5" t="s">
+      <c r="F53" s="2"/>
+    </row>
+    <row x14ac:dyDescent="0.25" r="54" customHeight="1" ht="15.75">
+      <c r="A54" s="1" t="s">
         <v>188</v>
       </c>
-      <c r="B54" s="6" t="s">
+      <c r="B54" s="2" t="s">
         <v>79</v>
       </c>
-      <c r="C54" s="10" t="s">
+      <c r="C54" s="3" t="s">
         <v>189</v>
       </c>
-      <c r="D54" s="14"/>
-      <c r="E54" s="7" t="s">
+      <c r="D54" s="4"/>
+      <c r="E54" s="3" t="s">
         <v>190</v>
       </c>
-      <c r="F54" s="11"/>
-    </row>
-    <row r="55" ht="15.75" customHeight="1">
-      <c r="A55" s="5" t="s">
+      <c r="F54" s="2"/>
+    </row>
+    <row x14ac:dyDescent="0.25" r="55" customHeight="1" ht="15.75">
+      <c r="A55" s="1" t="s">
         <v>191</v>
       </c>
-      <c r="B55" s="6" t="s">
+      <c r="B55" s="2" t="s">
         <v>79</v>
       </c>
-      <c r="C55" s="10" t="s">
+      <c r="C55" s="3" t="s">
         <v>192</v>
       </c>
-      <c r="D55" s="14"/>
-      <c r="E55" s="7" t="s">
+      <c r="D55" s="4"/>
+      <c r="E55" s="3" t="s">
         <v>193</v>
       </c>
-      <c r="F55" s="11"/>
-    </row>
-    <row r="56" ht="15.75" customHeight="1">
-      <c r="A56" s="5" t="s">
+      <c r="F55" s="2"/>
+    </row>
+    <row x14ac:dyDescent="0.25" r="56" customHeight="1" ht="15.75">
+      <c r="A56" s="1" t="s">
         <v>194</v>
       </c>
-      <c r="B56" s="6" t="s">
+      <c r="B56" s="2" t="s">
         <v>79</v>
       </c>
-      <c r="C56" s="10" t="s">
+      <c r="C56" s="3" t="s">
         <v>195</v>
       </c>
-      <c r="D56" s="14"/>
-      <c r="E56" s="7" t="s">
+      <c r="D56" s="4"/>
+      <c r="E56" s="3" t="s">
         <v>196</v>
       </c>
-      <c r="F56" s="11"/>
-    </row>
-    <row r="57" ht="15.75" customHeight="1">
-      <c r="A57" s="5" t="s">
+      <c r="F56" s="2"/>
+    </row>
+    <row x14ac:dyDescent="0.25" r="57" customHeight="1" ht="15.75">
+      <c r="A57" s="1" t="s">
         <v>197</v>
       </c>
-      <c r="B57" s="6" t="s">
+      <c r="B57" s="2" t="s">
         <v>79</v>
       </c>
-      <c r="C57" s="7" t="s">
+      <c r="C57" s="3" t="s">
         <v>198</v>
       </c>
-      <c r="D57" s="14"/>
-      <c r="E57" s="7" t="s">
+      <c r="D57" s="4"/>
+      <c r="E57" s="3" t="s">
         <v>199</v>
       </c>
-      <c r="F57" s="11"/>
-    </row>
-    <row r="58" ht="15.75" customHeight="1">
-      <c r="A58" s="5" t="s">
+      <c r="F57" s="2"/>
+    </row>
+    <row x14ac:dyDescent="0.25" r="58" customHeight="1" ht="15.75">
+      <c r="A58" s="1" t="s">
         <v>200</v>
       </c>
-      <c r="B58" s="6" t="s">
+      <c r="B58" s="2" t="s">
         <v>79</v>
       </c>
-      <c r="C58" s="7" t="s">
+      <c r="C58" s="3" t="s">
         <v>201</v>
       </c>
-      <c r="D58" s="14"/>
-      <c r="E58" s="7" t="s">
+      <c r="D58" s="4"/>
+      <c r="E58" s="3" t="s">
         <v>202</v>
       </c>
-      <c r="F58" s="11"/>
-    </row>
-    <row r="59" ht="15.75" customHeight="1">
-      <c r="A59" s="5" t="s">
+      <c r="F58" s="2"/>
+    </row>
+    <row x14ac:dyDescent="0.25" r="59" customHeight="1" ht="15.75">
+      <c r="A59" s="1" t="s">
         <v>203</v>
       </c>
-      <c r="B59" s="6" t="s">
+      <c r="B59" s="2" t="s">
         <v>45</v>
       </c>
-      <c r="C59" s="7" t="s">
+      <c r="C59" s="3" t="s">
         <v>204</v>
       </c>
-      <c r="D59" s="14"/>
-      <c r="E59" s="7" t="s">
+      <c r="D59" s="4"/>
+      <c r="E59" s="3" t="s">
         <v>205</v>
       </c>
-      <c r="F59" s="11"/>
-    </row>
-    <row r="60" ht="15.75" customHeight="1">
-      <c r="A60" s="5" t="s">
+      <c r="F59" s="2"/>
+    </row>
+    <row x14ac:dyDescent="0.25" r="60" customHeight="1" ht="15.75">
+      <c r="A60" s="1" t="s">
         <v>206</v>
       </c>
-      <c r="B60" s="6" t="s">
+      <c r="B60" s="2" t="s">
         <v>79</v>
       </c>
-      <c r="C60" s="7" t="s">
+      <c r="C60" s="3" t="s">
         <v>207</v>
       </c>
-      <c r="D60" s="14"/>
-      <c r="E60" s="7" t="s">
+      <c r="D60" s="4"/>
+      <c r="E60" s="3" t="s">
         <v>208</v>
       </c>
-      <c r="F60" s="11"/>
-    </row>
-    <row r="61" ht="15.75" customHeight="1">
-      <c r="A61" s="5" t="s">
+      <c r="F60" s="2"/>
+    </row>
+    <row x14ac:dyDescent="0.25" r="61" customHeight="1" ht="15.75">
+      <c r="A61" s="1" t="s">
         <v>209</v>
       </c>
-      <c r="B61" s="6" t="s">
+      <c r="B61" s="2" t="s">
         <v>45</v>
       </c>
-      <c r="C61" s="7" t="s">
+      <c r="C61" s="3" t="s">
         <v>210</v>
       </c>
-      <c r="D61" s="14"/>
-      <c r="E61" s="7" t="s">
+      <c r="D61" s="4"/>
+      <c r="E61" s="3" t="s">
         <v>211</v>
       </c>
-      <c r="F61" s="11"/>
-    </row>
-    <row r="62" ht="15.75" customHeight="1">
-      <c r="A62" s="5" t="s">
+      <c r="F61" s="2"/>
+    </row>
+    <row x14ac:dyDescent="0.25" r="62" customHeight="1" ht="15.75">
+      <c r="A62" s="1" t="s">
         <v>212</v>
       </c>
-      <c r="B62" s="6" t="s">
+      <c r="B62" s="2" t="s">
         <v>79</v>
       </c>
-      <c r="C62" s="7" t="s">
+      <c r="C62" s="3" t="s">
         <v>213</v>
       </c>
-      <c r="D62" s="14"/>
-      <c r="E62" s="7" t="s">
+      <c r="D62" s="4"/>
+      <c r="E62" s="3" t="s">
         <v>214</v>
       </c>
-      <c r="F62" s="9"/>
-    </row>
-    <row r="63" ht="15.75" customHeight="1">
-      <c r="A63" s="5" t="s">
+      <c r="F62" s="2"/>
+    </row>
+    <row x14ac:dyDescent="0.25" r="63" customHeight="1" ht="15.75">
+      <c r="A63" s="1" t="s">
         <v>215</v>
       </c>
-      <c r="B63" s="6" t="s">
+      <c r="B63" s="2" t="s">
         <v>45</v>
       </c>
-      <c r="C63" s="7" t="s">
+      <c r="C63" s="3" t="s">
         <v>216</v>
       </c>
-      <c r="D63" s="14"/>
-      <c r="E63" s="7" t="s">
+      <c r="D63" s="4"/>
+      <c r="E63" s="3" t="s">
         <v>217</v>
       </c>
-      <c r="F63" s="9"/>
-    </row>
-    <row r="64" ht="15.75" customHeight="1">
-      <c r="A64" s="5" t="s">
+      <c r="F63" s="2"/>
+    </row>
+    <row x14ac:dyDescent="0.25" r="64" customHeight="1" ht="15.75">
+      <c r="A64" s="1" t="s">
         <v>218</v>
       </c>
-      <c r="B64" s="6" t="s">
+      <c r="B64" s="2" t="s">
         <v>79</v>
       </c>
-      <c r="C64" s="7" t="s">
+      <c r="C64" s="3" t="s">
         <v>219</v>
       </c>
-      <c r="D64" s="14"/>
-      <c r="E64" s="7" t="s">
+      <c r="D64" s="4"/>
+      <c r="E64" s="3" t="s">
         <v>220</v>
       </c>
-      <c r="F64" s="11"/>
-    </row>
-    <row r="65" ht="15.75" customHeight="1">
-      <c r="A65" s="5" t="s">
+      <c r="F64" s="2"/>
+    </row>
+    <row x14ac:dyDescent="0.25" r="65" customHeight="1" ht="15.75">
+      <c r="A65" s="1" t="s">
         <v>221</v>
       </c>
-      <c r="B65" s="6" t="s">
+      <c r="B65" s="2" t="s">
         <v>7</v>
       </c>
-      <c r="C65" s="7" t="s">
+      <c r="C65" s="3" t="s">
         <v>222</v>
       </c>
-      <c r="D65" s="14"/>
-      <c r="E65" s="7" t="s">
+      <c r="D65" s="4"/>
+      <c r="E65" s="3" t="s">
         <v>223</v>
       </c>
-      <c r="F65" s="11"/>
-    </row>
-    <row r="66" ht="15.75" customHeight="1">
-      <c r="A66" s="5" t="s">
+      <c r="F65" s="2"/>
+    </row>
+    <row x14ac:dyDescent="0.25" r="66" customHeight="1" ht="15.75">
+      <c r="A66" s="1" t="s">
         <v>224</v>
       </c>
-      <c r="B66" s="6" t="s">
+      <c r="B66" s="2" t="s">
         <v>11</v>
       </c>
-      <c r="C66" s="7" t="s">
+      <c r="C66" s="3" t="s">
         <v>225</v>
       </c>
-      <c r="D66" s="8" t="s">
+      <c r="D66" s="3" t="s">
         <v>13</v>
       </c>
-      <c r="E66" s="7" t="s">
+      <c r="E66" s="3" t="s">
         <v>226</v>
       </c>
-      <c r="F66" s="9"/>
-    </row>
-    <row r="67" ht="15.75" customHeight="1">
-      <c r="A67" s="5" t="s">
+      <c r="F66" s="2"/>
+    </row>
+    <row x14ac:dyDescent="0.25" r="67" customHeight="1" ht="15.75">
+      <c r="A67" s="1" t="s">
         <v>227</v>
       </c>
-      <c r="B67" s="6" t="s">
+      <c r="B67" s="2" t="s">
         <v>11</v>
       </c>
-      <c r="C67" s="10" t="s">
+      <c r="C67" s="3" t="s">
         <v>228</v>
       </c>
-      <c r="D67" s="8" t="s">
+      <c r="D67" s="3" t="s">
         <v>17</v>
       </c>
-      <c r="E67" s="7" t="s">
+      <c r="E67" s="3" t="s">
         <v>22</v>
       </c>
-      <c r="F67" s="9"/>
-    </row>
-    <row r="68" ht="15.75" customHeight="1">
-      <c r="A68" s="5" t="s">
+      <c r="F67" s="2"/>
+    </row>
+    <row x14ac:dyDescent="0.25" r="68" customHeight="1" ht="15.75">
+      <c r="A68" s="1" t="s">
         <v>229</v>
       </c>
-      <c r="B68" s="6" t="s">
+      <c r="B68" s="2" t="s">
         <v>11</v>
       </c>
-      <c r="C68" s="10" t="s">
+      <c r="C68" s="3" t="s">
         <v>230</v>
       </c>
-      <c r="D68" s="8"/>
-      <c r="E68" s="7" t="s">
+      <c r="D68" s="4"/>
+      <c r="E68" s="3" t="s">
         <v>231</v>
       </c>
-      <c r="F68" s="9"/>
-    </row>
-    <row r="69" ht="15.75" customHeight="1">
-      <c r="A69" s="5" t="s">
+      <c r="F68" s="2"/>
+    </row>
+    <row x14ac:dyDescent="0.25" r="69" customHeight="1" ht="15.75">
+      <c r="A69" s="1" t="s">
         <v>232</v>
       </c>
-      <c r="B69" s="6" t="s">
+      <c r="B69" s="2" t="s">
         <v>24</v>
       </c>
-      <c r="C69" s="10" t="s">
+      <c r="C69" s="3" t="s">
         <v>233</v>
       </c>
-      <c r="D69" s="8" t="s">
+      <c r="D69" s="3" t="s">
         <v>26</v>
       </c>
-      <c r="E69" s="7" t="s">
+      <c r="E69" s="3" t="s">
         <v>234</v>
       </c>
-      <c r="F69" s="11"/>
-    </row>
-    <row r="70" ht="15.75" customHeight="1">
-      <c r="A70" s="5" t="s">
+      <c r="F69" s="2"/>
+    </row>
+    <row x14ac:dyDescent="0.25" r="70" customHeight="1" ht="15.75">
+      <c r="A70" s="1" t="s">
         <v>235</v>
       </c>
-      <c r="B70" s="6" t="s">
+      <c r="B70" s="2" t="s">
         <v>24</v>
       </c>
-      <c r="C70" s="10" t="s">
+      <c r="C70" s="3" t="s">
         <v>236</v>
       </c>
-      <c r="D70" s="8" t="s">
+      <c r="D70" s="3" t="s">
         <v>30</v>
       </c>
-      <c r="E70" s="7" t="s">
+      <c r="E70" s="3" t="s">
         <v>237</v>
       </c>
-      <c r="F70" s="9"/>
-    </row>
-    <row r="71" ht="15.75" customHeight="1">
-      <c r="A71" s="5" t="s">
+      <c r="F70" s="2"/>
+    </row>
+    <row x14ac:dyDescent="0.25" r="71" customHeight="1" ht="15.75">
+      <c r="A71" s="1" t="s">
         <v>238</v>
       </c>
-      <c r="B71" s="6" t="s">
+      <c r="B71" s="2" t="s">
         <v>41</v>
       </c>
-      <c r="C71" s="10" t="s">
+      <c r="C71" s="3" t="s">
         <v>239</v>
       </c>
-      <c r="D71" s="8"/>
-      <c r="E71" s="7" t="s">
+      <c r="D71" s="4"/>
+      <c r="E71" s="3" t="s">
         <v>240</v>
       </c>
-      <c r="F71" s="11"/>
-    </row>
-    <row r="72" ht="15.75" customHeight="1">
-      <c r="A72" s="5" t="s">
+      <c r="F71" s="2"/>
+    </row>
+    <row x14ac:dyDescent="0.25" r="72" customHeight="1" ht="15.75">
+      <c r="A72" s="1" t="s">
         <v>241</v>
       </c>
-      <c r="B72" s="6" t="s">
+      <c r="B72" s="2" t="s">
         <v>41</v>
       </c>
-      <c r="C72" s="10" t="s">
+      <c r="C72" s="3" t="s">
         <v>242</v>
       </c>
-      <c r="D72" s="8"/>
-      <c r="E72" s="7" t="s">
+      <c r="D72" s="4"/>
+      <c r="E72" s="3" t="s">
         <v>243</v>
       </c>
-      <c r="F72" s="11"/>
-    </row>
-    <row r="73" ht="15.75" customHeight="1">
-      <c r="A73" s="5" t="s">
+      <c r="F72" s="2"/>
+    </row>
+    <row x14ac:dyDescent="0.25" r="73" customHeight="1" ht="15.75">
+      <c r="A73" s="1" t="s">
         <v>244</v>
       </c>
-      <c r="B73" s="6" t="s">
+      <c r="B73" s="2" t="s">
         <v>79</v>
       </c>
-      <c r="C73" s="10" t="s">
+      <c r="C73" s="3" t="s">
         <v>245</v>
       </c>
-      <c r="D73" s="14"/>
-      <c r="E73" s="7" t="s">
+      <c r="D73" s="4"/>
+      <c r="E73" s="3" t="s">
         <v>246</v>
       </c>
-      <c r="F73" s="9"/>
-    </row>
-    <row r="74" ht="15.75" customHeight="1">
-      <c r="A74" s="5" t="s">
+      <c r="F73" s="2"/>
+    </row>
+    <row x14ac:dyDescent="0.25" r="74" customHeight="1" ht="15.75">
+      <c r="A74" s="1" t="s">
         <v>247</v>
       </c>
-      <c r="B74" s="6" t="s">
+      <c r="B74" s="2" t="s">
         <v>45</v>
       </c>
-      <c r="C74" s="10" t="s">
+      <c r="C74" s="3" t="s">
         <v>248</v>
       </c>
-      <c r="D74" s="8"/>
-      <c r="E74" s="7" t="s">
+      <c r="D74" s="4"/>
+      <c r="E74" s="3" t="s">
         <v>249</v>
       </c>
-      <c r="F74" s="11"/>
-    </row>
-    <row r="75" ht="15.75" customHeight="1">
-      <c r="A75" s="5" t="s">
+      <c r="F74" s="2"/>
+    </row>
+    <row x14ac:dyDescent="0.25" r="75" customHeight="1" ht="15.75">
+      <c r="A75" s="1" t="s">
         <v>250</v>
       </c>
-      <c r="B75" s="6" t="s">
+      <c r="B75" s="2" t="s">
         <v>45</v>
       </c>
-      <c r="C75" s="10" t="s">
+      <c r="C75" s="3" t="s">
         <v>251</v>
       </c>
-      <c r="D75" s="8"/>
-      <c r="E75" s="7" t="s">
+      <c r="D75" s="4"/>
+      <c r="E75" s="3" t="s">
         <v>252</v>
       </c>
-      <c r="F75" s="11"/>
-    </row>
-    <row r="76" ht="15.75" customHeight="1">
-      <c r="A76" s="5" t="s">
+      <c r="F75" s="2"/>
+    </row>
+    <row x14ac:dyDescent="0.25" r="76" customHeight="1" ht="15.75">
+      <c r="A76" s="1" t="s">
         <v>253</v>
       </c>
-      <c r="B76" s="6" t="s">
+      <c r="B76" s="2" t="s">
         <v>45</v>
       </c>
-      <c r="C76" s="10" t="s">
+      <c r="C76" s="3" t="s">
         <v>254</v>
       </c>
-      <c r="D76" s="10" t="s">
+      <c r="D76" s="3" t="s">
         <v>255</v>
       </c>
-      <c r="E76" s="7" t="s">
+      <c r="E76" s="3" t="s">
         <v>256</v>
       </c>
-      <c r="F76" s="11" t="s">
+      <c r="F76" s="2" t="s">
         <v>257</v>
       </c>
     </row>
-    <row r="77" ht="15.75" customHeight="1">
-      <c r="A77" s="5" t="s">
+    <row x14ac:dyDescent="0.25" r="77" customHeight="1" ht="15.75">
+      <c r="A77" s="1" t="s">
         <v>258</v>
       </c>
-      <c r="B77" s="6" t="s">
+      <c r="B77" s="2" t="s">
         <v>45</v>
       </c>
-      <c r="C77" s="10" t="s">
+      <c r="C77" s="3" t="s">
         <v>46</v>
       </c>
-      <c r="D77" s="8" t="s">
+      <c r="D77" s="3" t="s">
         <v>259</v>
       </c>
-      <c r="E77" s="7" t="s">
+      <c r="E77" s="3" t="s">
         <v>260</v>
       </c>
-      <c r="F77" s="11"/>
-    </row>
-    <row r="78" ht="15.75" customHeight="1">
-      <c r="A78" s="5" t="s">
+      <c r="F77" s="2"/>
+    </row>
+    <row x14ac:dyDescent="0.25" r="78" customHeight="1" ht="15.75">
+      <c r="A78" s="1" t="s">
         <v>261</v>
       </c>
-      <c r="B78" s="6" t="s">
+      <c r="B78" s="2" t="s">
         <v>50</v>
       </c>
-      <c r="C78" s="10" t="s">
+      <c r="C78" s="3" t="s">
         <v>262</v>
       </c>
-      <c r="D78" s="8"/>
-      <c r="E78" s="7"/>
-      <c r="F78" s="11" t="s">
+      <c r="D78" s="4"/>
+      <c r="E78" s="3" t="s">
         <v>263</v>
       </c>
-    </row>
-    <row r="79" ht="15.75" customHeight="1">
-      <c r="A79" s="5" t="s">
+      <c r="F78" s="2" t="s">
         <v>264</v>
       </c>
-      <c r="B79" s="6" t="s">
+    </row>
+    <row x14ac:dyDescent="0.25" r="79" customHeight="1" ht="15.75">
+      <c r="A79" s="1" t="s">
+        <v>265</v>
+      </c>
+      <c r="B79" s="2" t="s">
         <v>41</v>
       </c>
-      <c r="C79" s="10" t="s">
-        <v>265</v>
-      </c>
-      <c r="D79" s="8"/>
-      <c r="E79" s="7" t="s">
+      <c r="C79" s="3" t="s">
         <v>266</v>
       </c>
-      <c r="F79" s="9"/>
-    </row>
-    <row r="80" ht="15.75" customHeight="1">
-      <c r="A80" s="5" t="s">
+      <c r="D79" s="4"/>
+      <c r="E79" s="3" t="s">
         <v>267</v>
       </c>
-      <c r="B80" s="6" t="s">
+      <c r="F79" s="2"/>
+    </row>
+    <row x14ac:dyDescent="0.25" r="80" customHeight="1" ht="15.75">
+      <c r="A80" s="1" t="s">
+        <v>268</v>
+      </c>
+      <c r="B80" s="2" t="s">
         <v>41</v>
       </c>
-      <c r="C80" s="10" t="s">
-        <v>268</v>
-      </c>
-      <c r="D80" s="8" t="s">
+      <c r="C80" s="3" t="s">
         <v>269</v>
       </c>
-      <c r="E80" s="7" t="s">
+      <c r="D80" s="3" t="s">
         <v>270</v>
       </c>
-      <c r="F80" s="11" t="s">
+      <c r="E80" s="3" t="s">
         <v>271</v>
       </c>
-    </row>
-    <row r="81" ht="15.75" customHeight="1">
-      <c r="A81" s="5" t="s">
+      <c r="F80" s="2" t="s">
         <v>272</v>
       </c>
-      <c r="B81" s="6" t="s">
+    </row>
+    <row x14ac:dyDescent="0.25" r="81" customHeight="1" ht="15.75">
+      <c r="A81" s="1" t="s">
+        <v>273</v>
+      </c>
+      <c r="B81" s="2" t="s">
         <v>41</v>
       </c>
-      <c r="C81" s="10" t="s">
-        <v>268</v>
-      </c>
-      <c r="D81" s="8" t="s">
-        <v>273</v>
-      </c>
-      <c r="E81" s="7" t="s">
+      <c r="C81" s="3" t="s">
+        <v>269</v>
+      </c>
+      <c r="D81" s="3" t="s">
         <v>274</v>
       </c>
-      <c r="F81" s="11" t="s">
-        <v>271</v>
-      </c>
-    </row>
-    <row r="82" ht="15.75" customHeight="1">
-      <c r="A82" s="5" t="s">
+      <c r="E81" s="3" t="s">
         <v>275</v>
       </c>
-      <c r="B82" s="6" t="s">
+      <c r="F81" s="2" t="s">
+        <v>272</v>
+      </c>
+    </row>
+    <row x14ac:dyDescent="0.25" r="82" customHeight="1" ht="15.75">
+      <c r="A82" s="1" t="s">
+        <v>276</v>
+      </c>
+      <c r="B82" s="2" t="s">
         <v>41</v>
       </c>
-      <c r="C82" s="10" t="s">
-        <v>268</v>
-      </c>
-      <c r="D82" s="8" t="s">
-        <v>276</v>
-      </c>
-      <c r="E82" s="7" t="s">
+      <c r="C82" s="3" t="s">
+        <v>269</v>
+      </c>
+      <c r="D82" s="3" t="s">
         <v>277</v>
       </c>
-      <c r="F82" s="11" t="s">
-        <v>271</v>
-      </c>
-    </row>
-    <row r="83" ht="15.75" customHeight="1">
-      <c r="A83" s="5" t="s">
+      <c r="E82" s="3" t="s">
         <v>278</v>
       </c>
-      <c r="B83" s="6" t="s">
+      <c r="F82" s="2" t="s">
+        <v>272</v>
+      </c>
+    </row>
+    <row x14ac:dyDescent="0.25" r="83" customHeight="1" ht="15.75">
+      <c r="A83" s="1" t="s">
+        <v>279</v>
+      </c>
+      <c r="B83" s="2" t="s">
         <v>41</v>
       </c>
-      <c r="C83" s="10" t="s">
-        <v>268</v>
-      </c>
-      <c r="D83" s="8" t="s">
-        <v>279</v>
-      </c>
-      <c r="E83" s="7" t="s">
+      <c r="C83" s="3" t="s">
+        <v>269</v>
+      </c>
+      <c r="D83" s="3" t="s">
         <v>280</v>
       </c>
-      <c r="F83" s="11" t="s">
-        <v>271</v>
-      </c>
-    </row>
-    <row r="84" ht="15.75" customHeight="1">
-      <c r="A84" s="5" t="s">
+      <c r="E83" s="3" t="s">
         <v>281</v>
       </c>
-      <c r="B84" s="6" t="s">
+      <c r="F83" s="2" t="s">
+        <v>272</v>
+      </c>
+    </row>
+    <row x14ac:dyDescent="0.25" r="84" customHeight="1" ht="15.75">
+      <c r="A84" s="1" t="s">
+        <v>282</v>
+      </c>
+      <c r="B84" s="2" t="s">
         <v>41</v>
       </c>
-      <c r="C84" s="10" t="s">
-        <v>268</v>
-      </c>
-      <c r="D84" s="8" t="s">
-        <v>282</v>
-      </c>
-      <c r="E84" s="7" t="s">
+      <c r="C84" s="3" t="s">
+        <v>269</v>
+      </c>
+      <c r="D84" s="3" t="s">
         <v>283</v>
       </c>
-      <c r="F84" s="11" t="s">
-        <v>271</v>
-      </c>
-    </row>
-    <row r="85" ht="15.75" customHeight="1">
-      <c r="A85" s="5" t="s">
+      <c r="E84" s="3" t="s">
         <v>284</v>
       </c>
-      <c r="B85" s="6" t="s">
+      <c r="F84" s="2" t="s">
+        <v>272</v>
+      </c>
+    </row>
+    <row x14ac:dyDescent="0.25" r="85" customHeight="1" ht="15.75">
+      <c r="A85" s="1" t="s">
+        <v>285</v>
+      </c>
+      <c r="B85" s="2" t="s">
         <v>45</v>
       </c>
-      <c r="C85" s="7" t="s">
-        <v>285</v>
-      </c>
-      <c r="D85" s="8"/>
-      <c r="E85" s="7" t="s">
+      <c r="C85" s="3" t="s">
         <v>286</v>
       </c>
-      <c r="F85" s="11"/>
-    </row>
-    <row r="86" ht="15.75" customHeight="1">
-      <c r="A86" s="5" t="s">
+      <c r="D85" s="4"/>
+      <c r="E85" s="3" t="s">
         <v>287</v>
       </c>
-      <c r="B86" s="6" t="s">
+      <c r="F85" s="2"/>
+    </row>
+    <row x14ac:dyDescent="0.25" r="86" customHeight="1" ht="15.75">
+      <c r="A86" s="1" t="s">
+        <v>288</v>
+      </c>
+      <c r="B86" s="2" t="s">
         <v>45</v>
       </c>
-      <c r="C86" s="10" t="s">
-        <v>288</v>
-      </c>
-      <c r="D86" s="14"/>
-      <c r="E86" s="7" t="s">
+      <c r="C86" s="3" t="s">
         <v>289</v>
       </c>
-      <c r="F86" s="11"/>
-    </row>
-    <row r="87" ht="15.75" customHeight="1">
-      <c r="A87" s="5" t="s">
+      <c r="D86" s="4"/>
+      <c r="E86" s="3" t="s">
         <v>290</v>
       </c>
-      <c r="B87" s="6" t="s">
+      <c r="F86" s="2"/>
+    </row>
+    <row x14ac:dyDescent="0.25" r="87" customHeight="1" ht="15.75">
+      <c r="A87" s="1" t="s">
+        <v>291</v>
+      </c>
+      <c r="B87" s="2" t="s">
         <v>79</v>
       </c>
-      <c r="C87" s="10" t="s">
-        <v>291</v>
-      </c>
-      <c r="D87" s="8"/>
-      <c r="E87" s="7" t="s">
+      <c r="C87" s="3" t="s">
         <v>292</v>
       </c>
-      <c r="F87" s="9"/>
-    </row>
-    <row r="88" ht="15.75" customHeight="1">
-      <c r="A88" s="5" t="s">
+      <c r="D87" s="4"/>
+      <c r="E87" s="3" t="s">
         <v>293</v>
       </c>
-      <c r="B88" s="6" t="s">
+      <c r="F87" s="2"/>
+    </row>
+    <row x14ac:dyDescent="0.25" r="88" customHeight="1" ht="15.75">
+      <c r="A88" s="1" t="s">
+        <v>294</v>
+      </c>
+      <c r="B88" s="2" t="s">
         <v>79</v>
       </c>
-      <c r="C88" s="10" t="s">
-        <v>294</v>
-      </c>
-      <c r="D88" s="8"/>
-      <c r="E88" s="7" t="s">
+      <c r="C88" s="3" t="s">
         <v>295</v>
       </c>
-      <c r="F88" s="9"/>
-    </row>
-    <row r="89" ht="15.75" customHeight="1">
-      <c r="A89" s="5" t="s">
+      <c r="D88" s="4"/>
+      <c r="E88" s="3" t="s">
         <v>296</v>
       </c>
-      <c r="B89" s="6" t="s">
+      <c r="F88" s="2"/>
+    </row>
+    <row x14ac:dyDescent="0.25" r="89" customHeight="1" ht="15.75">
+      <c r="A89" s="1" t="s">
+        <v>297</v>
+      </c>
+      <c r="B89" s="2" t="s">
         <v>79</v>
       </c>
-      <c r="C89" s="10" t="s">
-        <v>297</v>
-      </c>
-      <c r="D89" s="8"/>
-      <c r="E89" s="7" t="s">
+      <c r="C89" s="3" t="s">
         <v>298</v>
       </c>
-      <c r="F89" s="11"/>
-    </row>
-    <row r="90" ht="15.75" customHeight="1">
-      <c r="A90" s="5" t="s">
+      <c r="D89" s="4"/>
+      <c r="E89" s="3" t="s">
         <v>299</v>
       </c>
-      <c r="B90" s="6" t="s">
+      <c r="F89" s="2"/>
+    </row>
+    <row x14ac:dyDescent="0.25" r="90" customHeight="1" ht="15.75">
+      <c r="A90" s="1" t="s">
+        <v>300</v>
+      </c>
+      <c r="B90" s="2" t="s">
         <v>79</v>
       </c>
-      <c r="C90" s="10" t="s">
-        <v>300</v>
-      </c>
-      <c r="D90" s="8"/>
-      <c r="E90" s="7" t="s">
+      <c r="C90" s="3" t="s">
         <v>301</v>
       </c>
-      <c r="F90" s="11"/>
-    </row>
-    <row r="91" ht="15.75" customHeight="1">
-      <c r="A91" s="5" t="s">
+      <c r="D90" s="4"/>
+      <c r="E90" s="3" t="s">
         <v>302</v>
       </c>
-      <c r="B91" s="6" t="s">
+      <c r="F90" s="2"/>
+    </row>
+    <row x14ac:dyDescent="0.25" r="91" customHeight="1" ht="90">
+      <c r="A91" s="1" t="s">
+        <v>303</v>
+      </c>
+      <c r="B91" s="2" t="s">
         <v>79</v>
       </c>
-      <c r="C91" s="10" t="s">
-        <v>303</v>
-      </c>
-      <c r="D91" s="8"/>
-      <c r="E91" s="7" t="s">
+      <c r="C91" s="3" t="s">
         <v>304</v>
       </c>
-      <c r="F91" s="9"/>
-    </row>
-    <row r="92" ht="15.75" customHeight="1">
-      <c r="A92" s="5" t="s">
+      <c r="D91" s="4"/>
+      <c r="E91" s="3" t="s">
         <v>305</v>
       </c>
-      <c r="B92" s="6" t="s">
+      <c r="F91" s="2"/>
+    </row>
+    <row x14ac:dyDescent="0.25" r="92" customHeight="1" ht="15.75">
+      <c r="A92" s="1" t="s">
+        <v>306</v>
+      </c>
+      <c r="B92" s="2" t="s">
         <v>79</v>
       </c>
-      <c r="C92" s="10" t="s">
-        <v>306</v>
-      </c>
-      <c r="D92" s="8"/>
-      <c r="E92" s="7" t="s">
+      <c r="C92" s="3" t="s">
         <v>307</v>
       </c>
-      <c r="F92" s="9"/>
+      <c r="D92" s="4"/>
+      <c r="E92" s="3" t="s">
+        <v>308</v>
+      </c>
+      <c r="F92" s="2"/>
     </row>
   </sheetData>
-  <dataValidations>
-    <dataValidation type="list" allowBlank="1" sqref="B2:B92">
-      <formula1>"ScenarioReference,Agenda,Act,Location,Enemy,Treachery,Asset,Story"</formula1>
-    </dataValidation>
-    <dataValidation allowBlank="1" showDropDown="1" sqref="A2:A92 D2:D92"/>
-  </dataValidations>
-  <drawing r:id="rId1"/>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <tableParts count="1">
-    <tablePart r:id="rId3"/>
+    <tablePart r:id="rId1"/>
   </tableParts>
 </worksheet>
 </file>